--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_07_Physical_Optics.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_07_Physical_Optics.xlsx
@@ -1168,11 +1168,6 @@
           <t>একটি বিন্দু আলোক উৎস থেকে নির্গত গোলকীয় তরঙ্গমুখ এবং একটি সুষম রৈখিক উৎস থেকে নির্গত বেলনাকার তরঙ্গমুখের জন্য তরঙ্গমুখে দূরত্বের সাথে তরঙ্গের তীব্রতা $I$ এবং বিস্তার $A$-এর নির্ভরতা যথাক্রমে কেমন হবে?</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>বিন্দু উৎসের ক্ষেত্রে শক্তি গোলকের পৃষ্ঠে ছড়ায়, ফলে ক্ষেত্রফল $S \propto r^2$। তীব্রতা $I = \frac{P}{4\pi r^2} \propto r^{-2}$ এবং বিস্তার $A \propto \frac{1}{r}$। রৈখিক উৎসের ক্ষেত্রে বেলনাকার তরঙ্গমুখের পৃষ্ঠের ক্ষেত্রফল $S = 2\pi r L \propto r$। সুতরাং তীব্রতা $I = \frac{P}{2\pi r L} \propto r^{-1}$ এবং বিস্তার $A \propto \frac{1}{\sqrt{r}}$।</t>
@@ -1218,11 +1213,6 @@
           <t>তরঙ্গমুখ এবং আলোক রশ্মির মধ্যবর্তী কোণ সর্বদা কত? সমতল তরঙ্গমুখ যখন সমতল সীমানায় আপাতিত হয়ে ঘন মাধ্যমে প্রতিসরিত হয়, তখন তরঙ্গমুখের প্রস্থের কী পরিবর্তন ঘটে?</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>হাইগেন্সের নীতি অনুযায়ী আলোক রশ্মি সর্বদা তরঙ্গমুখের উপর অভিলম্ব, তাই তাদের মধ্যবর্তী কোণ $90^\circ$। যখন কোণে আলো আপাতিত হয়, আপাতন কোণ $i$ ও প্রতিসরণ কোণ $r$। আপাতিত তরঙ্গমুখের প্রস্থ $w_1 = AB \cos i$ এবং প্রতিসরিত তরঙ্গমুখের প্রস্থ $w_2 = AB \cos r$। ঘন মাধ্যমে প্রতিসরণে $r &lt; i$, ফলে $\cos r &gt; \cos i$, যার দরুন প্রতিসরিত তরঙ্গমুখের প্রস্থ বৃদ্ধি পায় ($w_2 &gt; w_1$)।</t>
@@ -1268,11 +1258,6 @@
           <t>হাইগেন্সের গৌণ তরঙ্গিকা তত্ত্ব ব্যবহার করে স্নেলের প্রতিসরণ সূত্র ($\frac{\sin i}{\sin r} = \frac{v_1}{v_2}$) প্রতিপাদনের সময় নিউটনের কণিকা তত্ত্বের সাথে আলোর বেগ সম্পর্কিত কোন মৌলিক অসঙ্গতিটি অপসারিত হয়?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>নিউটনের কণিকা তত্ত্বে কণা আকর্ষণের ফলে ঘন মাধ্যমে আলোর বেগ বৃদ্ধির প্রস্তাব করা হয়েছিল ($v_2 &gt; v_1$), যা নির্দেশ করত $\mu = \frac{v_2}{v_1} &gt; 1$। কিন্তু হাইগেন্সের তরঙ্গ তত্ত্বে জ্যামিতিক প্রমাণ দেখায় $\frac{\sin i}{\sin r} = \frac{v_1}{v_2} = \mu$, অর্থাৎ ঘন মাধ্যমে আলোর বেগ হালকা মাধ্যম অপেক্ষা কম ($v_2 = \frac{v_1}{\mu} &lt; v_1$), যা পরবর্তীতে ফুকো (Foucault)-র পরীক্ষায় সরাসরি প্রমাণিত হয়।</t>
@@ -1318,11 +1303,6 @@
           <t>একটি সমতল তরঙ্গমুখ একটি পাতলা উত্তল লেন্সের প্রধান অক্ষের সমান্তরালে আপতিত হলে প্রতিসরিত তরঙ্গমুখের আকৃতি কেমন হবে এবং অবতল দর্পণে প্রতিফলিত হলে তরঙ্গমুখের বক্রতার কেন্দ্র কোথায় অবস্থিত হবে?</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>উত্তল লেন্সে সমান্তরাল রশ্মি অভিসারী হয়ে প্রধান ফোকাসে মিলিত হয়। সমতল তরঙ্গমুখটি ফোকাসমুখী অভিসারী গোলকীয় তরঙ্গমুখে (converging spherical wavefront) পরিণত হয় যার বক্রতার কেন্দ্র ফোকাসে অবস্থিত। অবতল দর্পণেও সমান্তরাল রশ্মি প্রতিফলিত হয়ে ফোকাসে অভিসৃত হয়, ফলে প্রতিফলিত তরঙ্গমুখটি ফোকাসমুখী অভিসারী গোলকীয় তরঙ্গমুখ হয় এবং এর বক্রতার কেন্দ্র দর্পণের প্রধান ফোকাস বিন্দুতেই অবস্থান করে।</t>
@@ -1368,11 +1348,6 @@
           <t>বায়ুতে $\lambda_0 = 600\text{ nm}$ তরঙ্গদৈর্ঘ্যের আলো প্রতিসরাঙ্ক $\mu = 1.5$ বিশিষ্ট কাঁচে প্রবেশ করলে এর কম্পাঙ্ক, তরঙ্গদৈর্ঘ্য এবং তরঙ্গের দশাবেগ কী অনুপাতে পরিবর্তিত হবে?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>প্রতিসরণের সময় আলোর কম্পাঙ্ক উৎসের বৈশিষ্ট্যের ওপর নির্ভরশীল হওয়ায় অপরিবর্তিত থাকে ($f' = f$)। কাঁচে তরঙ্গের বেগ $v = \frac{c}{\mu} = \frac{c}{1.5}$ এবং তরঙ্গদৈর্ঘ্য $\lambda = \frac{\lambda_0}{\mu} = \frac{600}{1.5} = 400\text{ nm}$। দশাবেগ ও তরঙ্গদৈর্ঘ্য উভয়ই মূল মানের $\frac{1}{1.5} = \frac{2}{3}$ গুণ হবে।</t>
@@ -1418,11 +1393,6 @@
           <t>হাইগেন্সের গৌণ তরঙ্গিকা তত্ত্বে কেবল অগ্রগামী তরঙ্গমুখ গঠিত হয় কিন্তু পশ্চাৎগামী তরঙ্গমুখ (backward wavefront) কেন গঠিত হয় না? পরবর্তীতে ফ্রেনেল এর কী গাণিতিক ব্যাখ্যা দেন?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>হাইগেন্স প্রাথমিক তত্ত্বে পশ্চাৎগামী তরঙ্গকে ইচ্ছাকৃতভাবে বাদ দিয়েছিলেন। পরবর্তীতে ফ্রেনেল অবলিকেটি ফ্যাক্টর (Obliquity factor বা tilt factor) $K(\theta) = \frac{1 + \cos\theta}{2}$ প্রবর্তন করেন, যেখানে $\theta$ হলো মূল অগ্রগামী দিকের সাথে উৎপন্ন কোণ। অগ্রগামী দিকে ($\theta = 0^\circ$) $K(0) = \frac{1+1}{2} = 1$, কিন্তু পশ্চাৎগামী দিকে ($\theta = 180^\circ$) $K(\pi) = \frac{1-1}{2} = 0$, যার ফলে বিপরীত দিকে তরঙ্গের বিস্তার সম্পূর্ণ শূন্য হয়ে যায়।</t>
@@ -1468,11 +1438,6 @@
           <t>একটি প্রিজমের প্রতিসারক কোণ $A$ এবং প্রতিসরাঙ্ক $\mu$। প্রিজমের একটি তলে সমতল তরঙ্গমুখ লম্বভাবে আপতিত হলে প্রিজম থেকে নির্গত তরঙ্গমুখটি আপতিত তরঙ্গমুখের সাপেক্ষে কত কোণে হেলে যাবে?</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>প্রথম তলে লম্বভাবে আপতিত হওয়ায় প্রথম তলে আপাতন কোণ $i_1 = 0$, প্রতিসরণ কোণ $r_1 = 0$। দ্বিতীয় তলে আপাতন কোণ $r_2 = A - r_1 = A$। দ্বিতীয় তল থেকে নির্গমন কোণ $i_2$ স্নেলের সূত্রানুযায়ী: $1 \cdot \sin i_2 = \mu \sin r_2 = \mu \sin A \Rightarrow i_2 = \arcsin(\mu \sin A)$। চ্যুতি কোণ $\delta = i_1 + i_2 - A = \arcsin(\mu \sin A) - A$। তরঙ্গমুখের দিক আলোর রশ্মির সাথে লম্ব থাকায় নির্গত তরঙ্গমুখটি আপাতিত তরঙ্গমুখের সাপেক্ষে ঠিক চ্যুতি কোণ $\delta$-তেই হেলে যাবে।</t>
@@ -1518,11 +1483,6 @@
           <t>$d$ পুরুত্বের এবং $\mu$ প্রতিসরাঙ্কের একটি মাধ্যমে আলো অতিক্রম করলে এর অপটিক্যাল পথ (Optical path) কত হবে এবং একই সময়ে আলো শূন্য মাধ্যমে যে দূরত্ব অতিক্রম করে তার সাথে এর সম্পর্ক কী?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>মাধ্যমে আলোর বেগ $v = \frac{c}{\mu}$। $d$ দূরত্ব যেতে প্রয়োজনীয় সময় $t = \frac{d}{v} = \frac{\mu d}{c}$। এই সময়ে আলো শূন্য মাধ্যমে দূরত্ব অতিক্রম করে $\Delta = c t = c \cdot \frac{\mu d}{c} = \mu d$। এই $\mu d$-কেই অপটিক্যাল পথ (বা আলোকীয় পথ) বলা হয়। সুতরাং অপটিক্যাল পথ = $\mu \times$ জ্যামিতিক পথ।</t>
@@ -1568,11 +1528,6 @@
           <t>একটি মাধ্যমে আলো সঞ্চালিত হচ্ছে যার তরঙ্গদৈর্ঘ্য $\lambda_0$ (শূন্যে) এবং প্রতিসরাঙ্ক $\mu$। দুটি আলোক রশ্মির মধ্যে অপটিক্যাল পথ পার্থক্য $\Delta$ হলে তাদের মধ্যে দশা পার্থক্য $\delta$-র সমীকরণ কী হবে?</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>মাধ্যমে তরঙ্গদৈর্ঘ্য $\lambda = \frac{\lambda_0}{\mu}$। জ্যামিতিক পথ পার্থক্য $\Delta x$ হলে অপটিক্যাল পথ পার্থক্য $\Delta = \mu \Delta x$। দশা পার্থক্য $\delta = \frac{2\pi}{\lambda} \Delta x = \frac{2\pi}{\lambda_0 / \mu} \Delta x = \frac{2\pi}{\lambda_0} (\mu \Delta x) = \frac{2\pi}{\lambda_0} \Delta$। অর্থাৎ অপটিক্যাল পথ পার্থক্যের সাথে শূন্য মাধ্যমের তরঙ্গদৈর্ঘ্যের মাধ্যমে সরাসরি দশা পার্থক্য নির্ণয় করা যায়।</t>
@@ -1618,11 +1573,6 @@
           <t>একটি বিন্দু উৎস $S$ প্রতিসরাঙ্ক $\mu$ বিশিষ্ট ঘন মাধ্যমে সমতল বিভেদতল থেকে $h$ গভীরে অবস্থিত। বিভেদতল থেকে নির্গত রশ্মিগুচ্ছের প্যারাক্সিয়াল (paraxial) অংশের নির্গত তরঙ্গমুখের আপাত বক্রতার ব্যাসার্ধ কত হবে?</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>ঘন মাধ্যম থেকে হালকা মাধ্যমে প্রতিসরণের ক্ষেত্রে প্যারাক্সিয়াল রশ্মির আপাত গভীরতা $h' = \frac{h}{\mu}$। নির্গত রশ্মিগুলো আপাত বিন্দু $S'$ থেকে অপসারিত হচ্ছে বলে মনে হয়। সুতরাং নির্গত গোলকীয় তরঙ্গমুখের বক্রতার কেন্দ্র $S'$ বিন্দুতে অবস্থিত এবং বিভেদতলে এর আপাত বক্রতার ব্যাসার্ধ হবে $R' = h' = \frac{h}{\mu}$।</t>
@@ -1668,11 +1618,6 @@
           <t>দুটি স্বাধীন লেজার রশ্মি কি সরাসরি সুসংগত উৎস (Coherent sources) হিসেবে টেকসই ব্যতিচার প্যাটার্ন তৈরি করতে পারে? সুসংগত দৈর্ঘ্য (Coherence length) $L_c$ এবং সুসংগত সময় (Coherence time) $\tau_c$-এর সম্পর্ক কী?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>দুটি স্বাধীন লেজার অত্যন্ত একবর্ণী হলেও তাদের মধ্যে স্বতঃস্ফূর্ত নিঃসরণের কারণে অনিয়মিত ও ক্ষণে ক্ষণে পরিবর্তিত দশা পরিবর্তন ঘটে, ফলে তাদের মধ্যে সময়-স্বাধীন স্থির দশা পার্থক্য থাকে না। টেকসই ব্যতিচারের জন্য দশা পার্থক্য $\Delta\phi$ সময়ের সাথে ধ্রুব থাকা আবশ্যক। সুসংগত দৈর্ঘ্য ও সুসংগত সময়ের সম্পর্ক হলো $L_c = c \tau_c$ যেখানে $c$ হলো আলোর বেগ এবং $\tau_c \approx \frac{1}{\Delta\nu}$।</t>
@@ -1718,11 +1663,6 @@
           <t>দুটি সুসংগত আলোক তরঙ্গের বিস্তার অনুপাত $A_1 : A_2 = 3 : 2$ হলে, তাদের ব্যতিচার প্যাটার্নে সর্বোচ্চ তীব্রতা ($I_{\max}$) ও সর্বনিম্ন তীব্রতা ($I_{\min}$)-এর অনুপাত এবং দৃশ্যমানতা (Fringe Visibility) $V$ কত হবে?</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>সর্বোচ্চ বিস্তার $A_{\max} = A_1 + A_2 = 3+2 = 5$ এবং সর্বনিম্ন বিস্তার $A_{\min} = A_1 - A_2 = 3-2 = 1$। তীব্রতার অনুপাত $\frac{I_{\max}}{I_{\min}} = \left(\frac{A_{\max}}{A_{\min}}\right)^2 = \left(\frac{5}{1}\right)^2 = 25 : 1$। দৃশ্যমানতা $V = \frac{I_{\max} - I_{\min}}{I_{\max} + I_{\min}} = \frac{25 - 1}{25 + 1} = \frac{24}{26} = \frac{12}{13} \approx 0.923$।</t>
@@ -1768,11 +1708,6 @@
           <t>ব্যতিচারের ফলে অন্ধকার ডোরার তীব্রতা শূন্য এবং উজ্জ্বল ডোরার তীব্রতা $4I_0$ হয়। এতে শক্তির সংরক্ষণ সূত্র লঙ্ঘিত হয় কি? গাণিতিক গড় তীব্রতা বের করে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>সমান তীব্রতার দুটি উৎস $I_0$ ব্যতিচার ঘটালে কোনো বিন্দুতে তীব্রতা $I = 4I_0 \cos^2\left(\frac{\delta}{2}\right)$। এক পর্যায়বৃত্তে $\cos^2\left(\frac{\delta}{2}\right)$-এর গড় মান $\frac{1}{2}$। সুতরাং গড় তীব্রতা $\langle I \rangle = 4I_0 \times \frac{1}{2} = 2I_0$। দুটি উৎসের শক্তির সাধারণ যোগফল $I_0 + I_0 = 2I_0$। অন্ধকার ডোরার স্থান থেকে অপসারিত শক্তি উজ্জ্বল ডোরায় স্থানান্তরিত হয়, ফলে ব্যতিচারে শক্তির সৃষ্টি বা বিনাশ হয় না, কেবল শক্তির পুনর্বন্টন ঘটে।</t>
@@ -1818,11 +1753,6 @@
           <t>প্রতিটির তীব্রতা $I_0$ বিশিষ্ট $N$ সংখ্যক স্বাধীন (অসুসংগত) আলোক তরঙ্গের উপরিপাতনে মোট তীব্রতা কত হবে এবং তারা সম্পূর্ণ সুসংগত ও সমদশাসম্পন্ন হলে মোট তীব্রতা কত হবে?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>অসুসংগত তরঙ্গের ক্ষেত্রে র্যান্ডম দশা পার্থক্যের কারণে ক্রস-টার্মের গড় শূন্য হয়, ফলে মোট তীব্রতা তীব্রতাগুলোর সরাসরি যোগফল: $I_{\text{incoherent}} = \sum_{i=1}^N I_0 = N I_0$। কিন্তু সুসংগত ও সমদশাসম্পন্ন হলে বিস্তার সরাসরি যোগ হয়: $A_{\text{total}} = N A_0$। যেহেতু $I \propto A^2$, মোট তীব্রতা $I_{\text{coherent}} = (N A_0)^2 = N^2 I_0$।</t>
@@ -1868,11 +1798,6 @@
           <t>আলোকীয় ব্যতিচার তৈরিতে 'তরঙ্গমুখ বিভাজন' (Division of Wavefront) এবং 'বিস্তার বিভাজন' (Division of Amplitude) পদ্ধতির মূল পার্থক্য কী এবং প্রতিটির একটি করে ক্লাসিক্যাল উদাহরণ দাও।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>তরঙ্গমুখ বিভাজনে একটি মূল তরঙ্গমুখের বিভিন্ন অংশকে দুটি বা ততোধিক গৌণ উৎসে বিভক্ত করা হয় (যেমন: ইয়ং-এর দ্বি-চির পরীক্ষা, ফ্রেনেলের বাইপ্রিজম, লয়েডস মিরর)। বিস্তার বিভাজনে আংশিক প্রতিফলন ও প্রতিসরণের মাধ্যমে একই তরঙ্গমুখের বিস্তারকে দুটি বা ততোধিক অংশে ভাগ করে পুনরায় উপরিপাতিত করা হয় (যেমন: পাতলা ফিল্মে ব্যতিচার, মাইকেলসন ইন্টারফেরোমিটার, নিউটনের বলয়)।</t>
@@ -1918,11 +1843,6 @@
           <t>লয়েডের একক দর্পণ (Lloyd's Mirror) পরীক্ষায় কেন্দ্রীয় ডোরার বৈশিষ্ট্য কী এবং সাধারণ YDSE-র কেন্দ্রীয় উজ্জ্বল ডোরার সাথে এর পার্থক্যের ভৌত কারণ কী?</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>লয়েডের দর্পণে একটি সরাসরি উৎস এবং দর্পণ থেকে প্রতিফলিত আপাত উৎসের মধ্যে ব্যতিচার ঘটে। প্রতিফলিত রশ্মি ঘন মাধ্যম (দর্পণ) থেকে প্রতিফলিত হওয়ায় স্টোকসের সূত্রানুযায়ী এতে অতিরিক্ত $\pi$ দশা পরিবর্তন (বা $\frac{\lambda}{2}$ পথ পার্থক্য) ঘটে। ফলে শূন্য পথ পার্থক্যের বিন্দুতে (কেন্দ্রীয় ডোরা) কার্যকর পথ পার্থক্য হয় $\frac{\lambda}{2}$, যা ধ্বংসাত্মক ব্যতিচারের শর্ত পূরণ করে। তাই কেন্দ্রীয় ডোরাটি উজ্জ্বল না হয়ে অন্ধকার (Dark fringe) হয়।</t>
@@ -1968,11 +1888,6 @@
           <t>একটি ফ্রেনেল বাইপ্রিজমের প্রতিসারক কোণ $\alpha$ (ক্ষুদ্র), প্রতিসরাঙ্ক $\mu$ এবং এটি একক চির থেকে $u$ দূরত্বে স্থাপিত। বাইপ্রিজম দ্বারা সৃষ্ট দুটি ভার্চুয়াল সুসংগত উৎসের মধ্যবর্তী দূরত্ব $d$-এর সমীকরণ কী হবে?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>বাইপ্রিজমের প্রতিটি প্রিজমার্ধের চ্যুতি কোণ $\delta = (\mu - 1)\alpha$। চির থেকে নির্গত রশ্মি $\delta$ কোণে বিচ্যুত হয়। ক্ষুদ্র কোণের জন্য ভার্চুয়াল উৎস দ্বয়ের স্থানচ্যুতি $\frac{d}{2} = u \delta = u(\mu - 1)\alpha$। সুতরাং দুটি ভার্চুয়াল উৎসের পারস্পরিক দূরত্ব $d = 2 u (\mu - 1)\alpha$, যেখানে $\alpha$ রেডিয়ানে প্রকাশিত।</t>
@@ -2069,11 +1984,6 @@
           <t>সমান তীব্রতা $I_0$-এর দুটি আলোক তরঙ্গের মধ্যে দশা পার্থক্য সময়ের সাথে সুষমভাবে পরিবর্তিত হয়ে $\Delta\phi(t) = \omega_0 t$ হলে ডিটেক্টরে পর্যবেক্ষিত গড় তীব্রতা কত হবে?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>যেকোনো মুহূর্তে তীব্রতা $I(t) = I_0 + I_0 + 2\sqrt{I_0 I_0}\cos(\omega_0 t) = 2I_0 [1 + \cos(\omega_0 t)]$। ডিটেক্টরের প্রতিক্রিয়াকাল $\tau$ যদি ব্যতিচার কম্পাঙ্কের পর্যায়কাল $T = \frac{2\pi}{\omega_0}$ অপেক্ষা অনেক বড় হয়, তবে পর্যবেক্ষিত তীব্রতা হবে সময়-গড়: $\langle I \rangle = 2I_0 [1 + \langle\cos(\omega_0 t)\rangle] = 2I_0 [1 + 0] = 2I_0$। ব্যতিচার ডোরার কোনো ওঠানামা দেখা যাবে না, সর্বত্র সমতীব্রতা বিরাজ করবে।</t>
@@ -2119,11 +2029,6 @@
           <t>একই রেখায় সমান দূরত্বে অবস্থিত তিনটি সুসংগত উৎস যাদের প্রত্যেকের তীব্রতা $I_0$ এবং পরপর দুটি উৎসের মধ্যে দশা পার্থক্য $\delta$। এদের উপরিপাতনে লব্ধি তীব্রতা $I(\delta)$-এর সাধারণ সমীকরণটি নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>তিনটি তরঙ্গের বিস্তার $A_0, A_0 e^{i\delta}, A_0 e^{i2\delta}$। লব্ধি বিস্তার $A = A_0 (1 + e^{i\delta} + e^{i2\delta}) = A_0 e^{i\delta} (e^{-i\delta} + 1 + e^{i\delta}) = A_0 e^{i\delta} (1 + 2\cos\delta)$। সুতরাং লব্ধি তীব্রতা $I = |A|^2 = A_0^2 (1 + 2\cos\delta)^2 = I_0 (1 + 2\cos\delta)^2$। (বিকল্প সমীকরণ: $I = I_0 \frac{\sin^2(3\delta/2)}{\sin^2(\delta/2)}$)।</t>
@@ -2169,11 +2074,6 @@
           <t>ইয়ং-এর দ্বি-চির পরীক্ষায় চিরদ্বয়ের মধ্যবর্তী দূরত্ব $d = 0.5\text{ mm}$, চির থেকে পর্দার দূরত্ব $D = 1.0\text{ m}$ এবং ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $\lambda = 500\text{ nm}$। পরপর দুটি উজ্জ্বল ডোরার রৈখিক দূরত্ব (ডোরার প্রস্থ) এবং কৌণিক বেধ কত?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>রৈখিক ডোরার প্রস্থ $\beta = \frac{\lambda D}{d} = \frac{500 \times 10^{-9}\text{ m} \times 1.0\text{ m}}{0.5 \times 10^{-3}\text{ m}} = 1.0 \times 10^{-3}\text{ m} = 1.0\text{ mm}$। কৌণিক বেধ $\theta = \frac{\beta}{D} = \frac{\lambda}{d} = \frac{500 \times 10^{-9}}{0.5 \times 10^{-3}} = 1.0 \times 10^{-3}\text{ rad} = 0.001\text{ rad}$ (বা $\approx 0.0573^\circ$)।</t>
@@ -2219,11 +2119,6 @@
           <t>YDSE-তে পর্দার কেন্দ্র থেকে যে বিন্দুতে পথ পার্থক্য $\frac{\lambda}{6}$, সেই বিন্দুতে তীব্রতা কেন্দ্রীয় চরম তীব্রতা $I_{\max}$-এর কত শতাংশ হবে?</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>পথ পার্থক্য $\Delta x = \frac{\lambda}{6}$ হলে দশা পার্থক্য $\delta = \frac{2\pi}{\lambda} \Delta x = \frac{2\pi}{\lambda} \cdot \frac{\lambda}{6} = \frac{\pi}{3} = 60^\circ$। তীব্রতার সমীকরণ $I = I_{\max} \cos^2\left(\frac{\delta}{2}\right) = I_{\max} \cos^2(30^\circ) = I_{\max} \left(\frac{\sqrt{3}}{2}\right)^2 = \frac{3}{4} I_{\max} = 75\%$।</t>
@@ -2269,11 +2164,6 @@
           <t>YDSE-তে $\lambda_1 = 600\text{ nm}$ এবং $\lambda_2 = 450\text{ nm}$ তরঙ্গদৈর্ঘ্যদ্বয় একসাথে ব্যবহার করা হলে, কেন্দ্রীয় চরম থেকে সর্বনিম্ন কত দূরত্বে উভয় তরঙ্গের উজ্জ্বল ডোরা সমাপতিত (coincide) হবে? ($D = 1\text{ m}, d = 1\text{ mm}$)</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>সমাপতনের শর্ত $n_1 \lambda_1 = n_2 \lambda_2 \Rightarrow \frac{n_1}{n_2} = \frac{\lambda_2}{\lambda_1} = \frac{450}{600} = \frac{3}{4}$। সর্বনিম্ন অ-শূন্য পূর্ণসংখ্যার অনুপাত $n_1 = 3, n_2 = 4$। অর্থাৎ $\lambda_1$-এর ৩য় উজ্জ্বল ডোরা এবং $\lambda_2$-এর ৪র্থ উজ্জ্বল ডোরা সমাপতিত হবে। কেন্দ্রীয় বিন্দু থেকে দূরত্ব $y = \frac{n_1 \lambda_1 D}{d} = \frac{3 \times 600 \times 10^{-9} \times 1}{1 \times 10^{-3}} = 1.8 \times 10^{-3}\text{ m} = 1.8\text{ mm}$।</t>
@@ -2319,11 +2209,6 @@
           <t>একটি সম্পূর্ণ YDSE সেটআপকে বায়ু মাধ্যম থেকে পানিতে ($\mu_w = \frac{4}{3}$) নিমজ্জিত করা হলে ডোরার প্রস্থ $\beta$ এবং কৌণিক বেধ $\theta$-র কী পরিবর্তন ঘটবে?</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>পানিতে নিমজ্জিত করলে আলোর বেগ ও তরঙ্গদৈর্ঘ্য হ্রাস পায়: $\lambda' = \frac{\lambda}{\mu_w} = \frac{3}{4}\lambda$। জ্যামিতিক মাত্রা $D$ এবং $d$ অপরিবর্তিত থাকে। নতুন ডোরার প্রস্থ $\beta' = \frac{\lambda' D}{d} = \frac{3}{4} \beta$ এবং কৌণিক বেধ $\theta' = \frac{\lambda'}{d} = \frac{3}{4} \theta$। অর্থাৎ উভয় রাশিই মূল মানের $\frac{3}{4}$ গুণ (বা $25\%$ হ্রাস পাবে) হবে।</t>
@@ -2369,11 +2254,6 @@
           <t>YDSE-তে চিরদ্বয়ের মধ্যবর্তী দূরত্ব $d = 3.5 \lambda$ হলে, পর্দায় মোট কতটি উজ্জ্বল ডোরা (কেন্দ্রীয় চরমসহ) পরিলক্ষিত হবে?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>উজ্জ্বল ডোরার পথ পার্থক্য $d \sin\theta = n \lambda \Rightarrow \sin\theta = \frac{n \lambda}{d}$। যেহেতু পর্দার সামনে $\sin\theta \le 1$, সুতরাং $\frac{n \lambda}{3.5 \lambda} \le 1 \Rightarrow n \le 3.5$। $n$ পূর্ণসংখ্যা হওয়ায় এর সম্ভাব্য মান $0, \pm 1, \pm 2, \pm 3$। মোট উজ্জ্বল ডোরার সংখ্যা $N = 2 \times 3 + 1 = 7$ টি। ($\theta = \pm 90^\circ$ অসীমে ধরা হয়)।</t>
@@ -2419,11 +2299,6 @@
           <t>YDSE-তে একটি চিরের প্রস্থ অপর চিরের দ্বিগুণ। চির দিয়ে নির্গত আলোর বিস্তার চিরের প্রস্থের সমানুপাতিক হলে, ডোরার চরম ও অবম তীব্রতার অনুপাত কত হবে?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>চিরের বিস্তার $w_1 = 2 w_2 \Rightarrow A_1 = 2 A_2$। ফলে তীব্রতা $I_1 \propto A_1^2 = 4 A_2^2 = 4 I_2$। চরম তীব্রতা $I_{\max} = (A_1 + A_2)^2 = (2A_2 + A_2)^2 = 9 A_2^2$। অবম তীব্রতা $I_{\min} = (A_1 - A_2)^2 = (2A_2 - A_2)^2 = A_2^2$। অনুপাত $\frac{I_{\max}}{I_{\min}} = \frac{9 A_2^2}{A_2^2} = 9 : 1$।</t>
@@ -2469,11 +2344,6 @@
           <t>YDSE-তে একবর্ণী আলোর পরিবর্তে সাদা আলো (শ্বেত আলো) ব্যবহার করলে পর্দার কেন্দ্রীয় ডোরা এবং তার পার্শ্ববর্তী অঞ্চলগুলোতে কী রূপ বৈচিত্র্য দেখা যাবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>কেন্দ্রীয় বিন্দুতে সকল তরঙ্গদৈর্ঘ্যের পথ পার্থক্য $\Delta x = 0$, ফলে সকল রঙের গঠনমূলক ব্যতিচার ঘটে কেন্দ্রটি উজ্জ্বল সাদা (White) দেখাবে। কেন্দ্রের নিকটবর্তী প্রথম ডোরার ক্ষেত্রে $\beta = \frac{\lambda D}{d}$ অনুযায়ী বেগুনী আলোর তরঙ্গদৈর্ঘ্য সবচেয়ে কম হওয়ায় কেন্দ্রের সবচেয়ে কাছে বেগুনী প্রান্ত এবং দূরে লাল প্রান্ত সৃষ্টি হবে। কয়েকটি রঙিন ব্যতিচার ডোরার পর বিভিন্ন রঙের ডোরার অতি-উপরিপাতনের দরুন সম্পূর্ণ পর্দা সমসত্ত্ব সাধারণ আলোকোজ্জ্বল দেখাবে।</t>
@@ -2519,11 +2389,6 @@
           <t>YDSE-তে পর্দাটি যদি চিরের তলের সাথে সমান্তরাল না হয়ে ক্ষুদ্র কোণ $\alpha$-তে আনত থাকে, তবে ডোরার প্রস্থ কি সুষম থাকবে? গাণিতিক যুক্তি দাও।</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>যদি পর্দা চিরের অক্ষের সাথে $\alpha$ কোণে হেলে থাকে, তবে পর্দার বিভিন্ন বিন্দুর জন্য কার্যকর দূরত্ব $D(y)$ ধ্রুবক থাকে না; বরং $D(y) = D_0 + y \tan\alpha$ আকারে পরিবর্তিত হয়। ফলে ডোরার প্রস্থ $\beta(y) = \frac{\lambda D(y)}{d}$ পর্দায় অবস্থানের সাথে সাথে বৃদ্ধি বা হ্রাস পায়, অর্থাৎ ব্যতিচার ডোরাগুলো আর সমান প্রস্থের (uniform) থাকে না।</t>
@@ -2569,11 +2434,6 @@
           <t>YDSE-তে পর্দায় সৃষ্ট ব্যতিচার ডোরাগুলোর প্রকৃত ত্রিমাত্রিক জ্যামিতিক আকৃতি কী এবং সাধারণ পর্যবেক্ষণে এদেরকে প্রায় সরলরৈখিক দেখায় কেন?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>দুটি সুসংগত বিন্দু উৎস $S_1$ ও $S_2$ থেকে নির্দিষ্ট পথ পার্থক্য $S_2 P - S_1 P = n \lambda = \text{constant}$ শর্ত পূরণকারী বিন্দুসমূহের সঞ্চারপথ মহাশূন্যে একটি দ্বিমুখী হাইপারবলয়েড (Hyperboloid of revolution)। সমতল পর্দা যখন এই হাইপারবলয়েডকে সমান্তরালে ছেদ করে, তখন ছেদরেখাটি হাইপারবোলা (অধিবৃত্ত) হয়। তবে চিরের ব্যবধান $d$ যদি পর্দা থেকে দূরত্ব $D$-এর তুলনায় অত্যন্ত ক্ষুদ্র হয় ($d \ll D$), তবে কেন্দ্রীয় অঞ্চলের ক্ষুদ্র অংশে হাইপারবোলার বক্রতা নগণ্য হয় এবং ডোরাগুলোকে প্রায় সমান্তরাল সরলরেখা মনে হয়।</t>
@@ -2619,11 +2479,6 @@
           <t>YDSE-তে একটি চির সম্পূর্ণ কালো কালি দিয়ে বন্ধ করে দিলে পর্দায় কী ঘটবে? ডোরার তীব্রতা ও বিন্যাসের পরিবর্তন ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>একটি চির বন্ধ করে দিলে দুটি উৎসের মধ্যে ব্যতিচার সম্পূর্ণরূপে বন্ধ হয়ে যাবে। তখন পর্দায় কেবল খোলা চিরটির জন্য ফ্রনহফার অপবর্তন প্যাটার্ন (Diffraction pattern) বা একটি প্রশস্ত কেন্দ্রীয় অপবর্তন অঞ্চল দেখা যাবে। কোনো সূক্ষ্ম ব্যতিচার ডোরা থাকবে না এবং তীব্রতা ধ্রুব $4I_0$ থেকে হ্রাস পেয়ে একক চিরের তীব্রতা $I_0$-তে নেমে আসবে।</t>
@@ -2669,11 +2524,6 @@
           <t>YDSE-তে একটি চিরের সামনে $t$ পুরুত্বের ও $\mu$ প্রতিসরাঙ্কের একটি পাতলা কাঁচের পাত রাখলে কেন্দ্রীয় উজ্জ্বল ডোরাটি যে দূরত্বে সরে যায়, তার সমীকরণ কী?</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>কাঁচের পাত রাখলে ঐ পথটিতে অতিরিক্ত অপটিক্যাল পথ পার্থক্য তৈরি হয় $\Delta = (\mu - 1)t$। কেন্দ্রীয় উজ্জ্বল ডোরা পেতে মোট পথ পার্থক্য শূন্য হতে হবে: $\frac{d y_0}{D} - (\mu - 1)t = 0 \Rightarrow y_0 = \frac{D}{d}(\mu - 1)t$। যেহেতু ডোরার প্রস্থ $\beta = \frac{\lambda D}{d}$, সুতরাং স্থানান্তরকে ডোরার সংখ্যায় লিখলে $y_0 = \frac{\beta}{\lambda}(\mu - 1)t$ বা স্থানান্তরিত ডোরার সংখ্যা $N = \frac{(\mu - 1)t}{\lambda}$।</t>
@@ -2719,11 +2569,6 @@
           <t>YDSE-তে চির $S_1$-এর সামনে $t_1$ পুরুত্বের ও $\mu_1$ প্রতিসরাঙ্কের পাত এবং চির $S_2$-এর সামনে $t_2$ পুরুত্বের ও $\mu_2$ প্রতিসরাঙ্কের পাত রাখলে কেন্দ্রীয় ডোরার শিফট কত হবে?</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>উভয় পাতের কারণে অতিরিক্ত পথ পার্থক্য সৃষ্টি হয় $\Delta = [(\mu_1 - 1)t_1 - (\mu_2 - 1)t_2]$। কেন্দ্রীয় ডোরার নতুন অবস্থানের জন্য $\frac{d y_0}{D} = [(\mu_1 - 1)t_1 - (\mu_2 - 1)t_2]$। অতএব $y_0 = \frac{D}{d} [(\mu_1 - 1)t_1 - (\mu_2 - 1)t_2]$। যদি $(\mu_1 - 1)t_1 &gt; (\mu_2 - 1)t_2$ হয়, তবে শিফট $S_1$-এর দিকে ঘটবে।</t>
@@ -2769,11 +2614,6 @@
           <t>YDSE-তে একটি চিরের সামনে পাতলা স্বচ্ছ পাত রাখলে ব্যতিচার ডোরার প্রস্থ $\beta$-র কি কোনো পরিবর্তন ঘটে? এর কারণ কী?</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>স্বচ্ছ পাত রাখলে প্রতিটি বিন্দুর অপটিক্যাল পথ পার্থক্যে একটি ধ্রুব রাশি $(\mu - 1)t$ যোগ হয়: $\Delta x = \frac{d y}{D} - (\mu - 1)t$। পরপর দুটি ডোরার ব্যবধান $\Delta y = y_{n+1} - y_n = \frac{\lambda D}{d} = \beta$। যেহেতু শিফট ধ্রুবক এবং প্রতিটি ডোরার জন্য সমান, তাই সম্পূর্ণ প্যাটার্নটি অক্ষত অবস্থায় একপাশে সরে যায় কিন্তু ডোরার প্রস্থ $\beta$ অপরিবর্তিত থাকে।</t>
@@ -2819,11 +2659,6 @@
           <t>তরঙ্গদৈর্ঘ্য $\lambda = 600\text{ nm}$। একটি চিরের সামনে $t = 6\ \mu\text{m}$ পুরুত্বের একটি পাত স্থাপন করায় কেন্দ্রীয় চরমটি পূর্বের ৫ম উজ্জ্বল ডোরার স্থানে চলে গেল। পাতের প্রতিসরাঙ্ক $\mu$ কত?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>কেন্দ্রীয় চরম ৫ম ডোরার স্থানে যাওয়ার অর্থ স্থানান্তরিত ডোরার সংখ্যা $N = 5$। সূত্রানুযায়ী, $(\mu - 1)t = N \lambda \Rightarrow \mu - 1 = \frac{N \lambda}{t} = \frac{5 \times 600 \times 10^{-9}\text{ m}}{6 \times 10^{-6}\text{ m}} = \frac{3 \times 10^{-6}}{6 \times 10^{-6}} = 0.5$। অতএব পাতের প্রতিসরাঙ্ক $\mu = 1 + 0.5 = 1.5$।</t>
@@ -2869,11 +2704,6 @@
           <t>YDSE-তে আলো যদি চিরের তলের অভিলম্বের সাথে $\alpha$ কোণে তির্যকভাবে আপতিত হয়, তবে কেন্দ্রীয় ডোরার কৌণিক অবস্থান অক্ষের সাপেক্ষে কত হবে?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>চিরদ্বয়ে পৌঁছার পূর্বেই আলোক তরঙ্গের মধ্যে প্রাথমিক পথ পার্থক্য তৈরি হয় $\Delta x_1 = d \sin\alpha$। পর্দায় $P$ বিন্দুতে পৌঁছাতে অতিরিক্ত পথ পার্থক্য $\Delta x_2 = d \sin\theta$। মোট পথ পার্থক্য $\Delta x = d \sin\theta - d \sin\alpha$। কেন্দ্রীয় চরমের জন্য $\Delta x = 0 \Rightarrow d \sin\theta = d \sin\alpha \Rightarrow \theta = \alpha$ (বিপরীত পাশে $\theta = -\alpha$)। অর্থাৎ কেন্দ্রীয় ডোরাটি মূল অক্ষ থেকে $\alpha$ কোণে নিচে বা বিপরীতে সরে যাবে।</t>
@@ -2919,11 +2749,6 @@
           <t>একটি একক উৎস $S$ চিরদ্বয়ের সংযোগকারী রেখার লম্ব সমদ্বিখণ্ডকের উপর অবস্থিত ছিল। উৎসটিকে অক্ষের সাথে লম্বভাবে $y_s$ দূরত্বে সরানো হলে কেন্দ্রীয় চরম পর্দায় কত দূরত্বে এবং কোন দিকে সরবে?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>উৎসটিকে $y_s$ সরানো হলে প্রাথমিক চির থেকে চিরদ্বয়ে পৌঁছানোর পথ পার্থক্য $\Delta x_s \approx \frac{d y_s}{s}$, যেখানে $s$ হলো উৎস থেকে চিরের দূরত্ব। পর্দায় কেন্দ্রীয় চরমের জন্য নেট পথ পার্থক্য শূন্য হতে হবে: $\frac{d y}{D} + \frac{d y_s}{s} = 0 \Rightarrow y = -\frac{D}{s} y_s$। অর্থাৎ উৎসটিকে যেদিকে সরানো হয়, কেন্দ্রীয় চরম পর্দায় তার ঠিক বিপরীত দিকে $y = \frac{D}{s} y_s$ দূরত্বে সরে যায়।</t>
@@ -2969,11 +2794,6 @@
           <t>একটি মাইকেলসন ব্যতিচারমাপে $\lambda = 500\text{ nm}$ আলো ব্যবহার করা হয়েছে। সচল দর্পণটিকে কত দূরত্ব সরালে দৃষ্টিরেখা দিয়ে $N = 200$ টি ব্যতিচার ডোরা অতিক্রম করবে?</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>মাইকেলসন ইন্টারফেরোমিটারে দর্পণ $d$ দূরত্ব সরলে আলোক রশ্মির পথ পার্থক্যের পরিবর্তন হয় $\Delta x = 2d$ (যেহেতু আলো গিয়ে আবার ফিরে আসে)। ফলে ডোরার শিফটের সম্পর্ক $2d = N \lambda \Rightarrow d = \frac{N \lambda}{2}$। মান বসিয়ে: $d = \frac{200 \times 500 \times 10^{-9}\text{ m}}{2} = 5.0 \times 10^{-5}\text{ m} = 0.05\text{ mm} = 50\ \mu\text{m}$।</t>
@@ -3019,11 +2839,6 @@
           <t>মাইকেলসন ইন্টারফেরোমিটারের একটি বাহুতে $L = 10\text{ cm}$ দীর্ঘ একটি ফাঁকা নলের মধ্যে ধীরে ধীরে গ্যাস প্রবেশ করানোর ফলে $N = 150$ টি ডোরা সরে যায়। আলোর তরঙ্গদৈর্ঘ্য $\lambda = 600\text{ nm}$ হলে গ্যাসের প্রতিসরাঙ্ক কত?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>নলের মধ্য দিয়ে আলো দুইবার অতিক্রম করায় পথ পার্থক্যের পরিবর্তন $\Delta x = 2(\mu - 1)L$। সূত্রানুযায়ী, $2(\mu - 1)L = N \lambda \Rightarrow \mu - 1 = \frac{N \lambda}{2L}$। মান বসিয়ে: $\mu - 1 = \frac{150 \times 600 \times 10^{-9}\text{ m}}{2 \times 0.1\text{ m}} = \frac{9.0 \times 10^{-5}}{0.2} = 4.5 \times 10^{-4}$। সুতরাং গ্যাসের প্রতিসরাঙ্ক $\mu = 1 + 0.00045 = 1.00045$।</t>
@@ -3069,11 +2884,6 @@
           <t>YDSE-তে একটি চিরের সামনে এমন একটি পাতলা পাত রাখা হলো যা আলোর বিস্তারকে $50\%$ শোষণ করে। ব্যতিচার ডোরার দৃশ্যমানতা $V$ কত হবে?</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>একটি চিরের বিস্তার $A_1 = A_0$ এবং অপর চিরের বিস্তার $A_2 = 0.5 A_0$। সর্বোচ্চ বিস্তার $A_{\max} = 1.5 A_0 \Rightarrow I_{\max} = 2.25 I_0$। সর্বনিম্ন বিস্তার $A_{\min} = 0.5 A_0 \Rightarrow I_{\min} = 0.25 I_0$। দৃশ্যমানতা $V = \frac{I_{\max} - I_{\min}}{I_{\max} + I_{\min}} = \frac{2.25 - 0.25}{2.25 + 0.25} = \frac{2.0}{2.5} = 0.8$ বা $80\%$।</t>
@@ -3170,11 +2980,6 @@
           <t>$\mu$ প্রতিসরাঙ্ক ও $t$ পুরুত্বের একটি পাতলা তেলের ফিল্মের ওপর $r$ প্রতিসরণ কোণে আলো আপতিত হলে প্রতিফলিত আলোয় গঠনমূলক ব্যতিচারের শর্ত $2\mu t \cos r = (2n-1)\frac{\lambda}{2}$ হয় কেন? স্বাভাবিক শর্ত থেকে পার্থক্যের কারণ কী?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>পাতলা ফিল্মের ক্ষেত্রে জ্যামিতিক অপটিক্যাল পথ পার্থক্য $2\mu t \cos r$। কিন্তু ঘন মাধ্যমের উপরিপৃষ্ঠ থেকে আলো প্রতিফলিত হওয়ার সময় স্টোকসের সম্পর্ক অনুযায়ী প্রতিফলিত তরঙ্গে অতিরিক্ত $\pi$ দশা পরিবর্তন ঘটে, যা $\frac{\lambda}{2}$ অতিরিক্ত পথ পার্থক্যের সমতুল্য। ফলে মোট পথ পার্থক্য হয় $2\mu t \cos r - \frac{\lambda}{2}$ বা $2\mu t \cos r + \frac{\lambda}{2}$। গঠনমূলক ব্যতিচারের জন্য $\Delta_{\text{net}} = n\lambda \Rightarrow 2\mu t \cos r = (2n-1)\frac{\lambda}{2}$।</t>
@@ -3220,11 +3025,6 @@
           <t>দিনের আলোয় সাবানের বুদবুদ রঙিন দেখায় কেন এবং সাবানের বুদবুদের প্রাচীর ফেটে যাওয়ার পূর্বমুহূর্তে অত্যন্ত পাতলা ($t \ll \lambda$) হলে তা অন্ধকার দেখায় কেন?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>সাবানের ফিল্মে সূর্যালোক পড়লে এর উপরের ও নিচের পৃষ্ঠ থেকে প্রতিফলিত রশ্মিগুলোর মধ্যে ব্যতিচার ঘটে। ভিন্ন ভিন্ন তরঙ্গদৈর্ঘ্যের জন্য গঠনমূলক ব্যতিচারের শর্ত ভিন্ন ভিন্ন কোণে পূরণ হওয়ায় বুদবুদটি রঙিন দেখায়। কিন্তু যখন প্রাচীরটি অত্যন্ত পাতলা হয় ($t \to 0$), তখন জ্যামিতিক পথ পার্থক্য $2\mu t \cos r \to 0$। কেবল উপরিপৃষ্ঠের প্রতিফলনের কারণে $\frac{\lambda}{2}$ পথ পার্থক্য বজায় থাকে। ফলে দৃশ্যমান সকল আলোর জন্য ধ্বংসাত্মক ব্যতিচার ঘটে এবং ফিল্মটি সম্পূর্ণ অন্ধকার (Black film) দেখায়।</t>
@@ -3270,11 +3070,6 @@
           <t>কাঁচের ($\mu_g = 1.5$) ওপর $\text{MgF}_2$ ($\mu_f = 1.38$) দিয়ে প্রতিফলন-বিরোধী কোটিং তৈরি করতে $\lambda = 550\text{ nm}$ আলোর জন্য আবরণের সর্বনিম্ন পুরুত্ব কত হওয়া উচিত?</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>এখানে বায়ু ($\mu_0 = 1$), কোটিং ($\mu_f = 1.38$), এবং কাঁচ ($\mu_g = 1.5$)। যেহেতু $\mu_0 &lt; \mu_f &lt; \mu_g$, তাই বায়ু-কোটিং এবং কোটিং-কাঁচ উভয় বিভেদতলেই ঘন মাধ্যম থেকে প্রতিফলন ঘটে এবং উভয় ক্ষেত্রেই $\pi$ দশা পরিবর্তন ঘটে। ফলে অতিরিক্ত দশাজনিত কোনো নিট পথ পার্থক্য থাকে না। প্রতিফলন ধ্বংসের (ধ্বংসাত্মক ব্যতিচার) জন্য জ্যামিতিক পথ পার্থক্য হতে হবে: $2\mu_f t = \frac{\lambda}{2} \Rightarrow t_{\min} = \frac{\lambda}{4\mu_f} = \frac{550\text{ nm}}{4 \times 1.38} = \frac{550}{5.52}\text{ nm} \approx 99.64\text{ nm}$।</t>
@@ -3320,11 +3115,6 @@
           <t>ক্ষুদ্র কোণ $\theta$ বিশিষ্ট একটি কীলকাকার (Wedge-shaped) বায়ু ফিল্মের ওপর লম্বভাবে $\lambda$ তরঙ্গদৈর্ঘ্যের আলো আপতিত হলে পরপর দুটি অন্ধকার ডোরার রৈখিক ব্যবধান $w$-এর সমীকরণ কী হবে?</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>কীলকাকার ফিল্মে অন্ধকার ডোরার শর্ত $2 t_n = n \lambda$। শীর্ষবিন্দু থেকে $x_n$ দূরত্বে পুরুত্ব $t_n = x_n \tan\theta \approx x_n \theta$। অতএব $2 x_n \theta = n \lambda \Rightarrow x_n = \frac{n \lambda}{2\theta}$। পরপর দুটি ডোরার রৈখিক ব্যবধান $w = x_{n+1} - x_n = \frac{(n+1)\lambda}{2\theta} - \frac{n \lambda}{2\theta} = \frac{\lambda}{2\theta}$।</t>
@@ -3370,11 +3160,6 @@
           <t>প্রতিফলিত আলোয় পর্যবেক্ষণে নিউটনের বলয় (Newton's Rings) পরীক্ষায় কেন্দ্রীয় বিন্দুটি সর্বদা অন্ধকার দেখায় কেন? প্রতিসারিত আলোয় দেখলে এটি কেমন দেখাবে?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>লেন্স ও কাঁচের প্লেটের স্পর্শবিন্দুতে বায়ু ফিল্মের পুরুত্ব $t = 0$। প্রতিফলিত রশ্মি দুটির মধ্যে কাঁচের সমতল প্লেট থেকে প্রতিফলনে অতিরিক্ত $\pi$ দশা পরিবর্তন (বা $\frac{\lambda}{2}$ পথ পার্থক্য) ঘটে। ফলে স্পর্শবিন্দুতে কার্যকর পথ পার্থক্য ঠিক $\frac{\lambda}{2}$, যা ধ্বংসাত্মক ব্যতিচারের শর্ত তৈরি করে কেন্দ্রকে অন্ধকার করে। প্রতিসারিত আলোর ক্ষেত্রে কোনো অতিরিক্ত দশা পরিবর্তন না থাকায় কার্যকর পথ পার্থক্য শূন্য হয় এবং কেন্দ্রটি উজ্জ্বল (Bright) দেখায়।</t>
@@ -3420,11 +3205,6 @@
           <t>নিউটনের বলয় পরীক্ষায় ব্যবহৃত সমতল-উত্তল লেন্সের বক্রতার ব্যাসার্ধ $R$ এবং আলোর তরঙ্গদৈর্ঘ্য $\lambda$। প্রতিফলিত আলোয় $n$-তম অন্ধকার বলয়ের ব্যাস $D_n$-এর সমীকরণ প্রতিপাদন করে দেখাও যে ব্যাস স্বাভাবিক সংখ্যার বর্গমূলের সমানুপাতিক।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>বৃত্তাকার জ্যামিতি হতে $r_n^2 = 2 R t_n$। অন্ধকার বলয়ের শর্ত $2 t_n = n \lambda \Rightarrow t_n = \frac{n\lambda}{2}$। সুতরাং $r_n^2 = 2 R \left(\frac{n\lambda}{2}\right) = n R \lambda$। ব্যাস $D_n = 2 r_n = 2 \sqrt{n R \lambda} = \sqrt{4 n R \lambda} \propto \sqrt{n}$। অর্থাৎ অন্ধকার বলয়ের ব্যাস স্বাভাবিক সংখ্যার বর্গমূলের সমানুপাতিক ($D_n \propto \sqrt{n}$)।</t>
@@ -3470,11 +3250,6 @@
           <t>নিউটনের বলয় সেটআপে লেন্স ও কাঁচের প্লেটের মধ্যকার বায়ু স্তরের স্থানে $\mu$ প্রতিসরাঙ্কের তরল প্রবেশ করালে বলয়গুলোর ব্যাসের কী রূপ পরিবর্তন ঘটবে?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>তরল প্রবেশ করালে মাধ্যমে তরঙ্গদৈর্ঘ্য $\lambda' = \frac{\lambda}{\mu}$ হয়ে যায়। $n$-তম অন্ধকার বলয়ের ব্যাসের সমীকরণ দাঁড়ায় $D_n' = 2\sqrt{\frac{n R \lambda}{\mu}} = \frac{D_n}{\sqrt{\mu}}$। যেহেতু $\mu &gt; 1$, তাই $D_n' &lt; D_n$, অর্থাৎ বলয়গুলো সংকুচিত হয়ে কেন্দ্রের দিকে চলে আসবে এবং তাদের ব্যাস $\frac{1}{\sqrt{\mu}}$ গুণ হ্রাস পাবে।</t>
@@ -3520,11 +3295,6 @@
           <t>নিউটনের বলয় পরীক্ষায় $m$-তম এবং $n$-তম অন্ধকার বলয়ের ব্যাস যথাক্রমে $D_m$ ও $D_n$ ($m &gt; n$)। লেন্সের বক্রতার ব্যাসার্ধ $R$ হলে আলোর তরঙ্গদৈর্ঘ্য $\lambda$-র সমীকরণ কী হবে?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>আমরা জানি $D_m^2 = 4 m R \lambda$ এবং $D_n^2 = 4 n R \lambda$। এদের বিয়োগফল: $D_m^2 - D_n^2 = 4(m - n)R \lambda$। অতএব আলোর তরঙ্গদৈর্ঘ্য $\lambda = \frac{D_m^2 - D_n^2}{4(m - n)R}$। এই সূত্রে স্পর্শবিন্দুর শূন্য ত্রুটি স্বয়ংক্রিয়ভাবে অপসারিত হয়।</t>
@@ -3570,11 +3340,6 @@
           <t>নিউটনের বলয়ে কেন্দ্র থেকে বাইরের দিকে অগ্রসর হলে পরপর দুটি অন্ধকার বলয়ের মধ্যকার দূরত্ব বা ব্যবধান ক্রমশ হ্রাস পায় কেন?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>$n$-তম বলয়ের ব্যাসার্ধ $r_n \propto \sqrt{n}$। পরপর দুটি বলয়ের দূরত্বের ব্যবধান $\Delta r = r_{n+1} - r_n \propto (\sqrt{n+1} - \sqrt{n}) = \frac{1}{\sqrt{n+1} + \sqrt{n}}$। $n$-এর মান বৃদ্ধি পেলে হর বৃদ্ধি পায়, ফলে $\Delta r$-এর মান ক্রমাগত হ্রাস পায়। অর্থাৎ কেন্দ্র থেকে বাইরের দিকে বলয়গুলো ক্রমশ ঘনসন্নিবিষ্ট (closer together) হতে থাকে।</t>
@@ -3620,11 +3385,6 @@
           <t>নিউটনের বলয় পরীক্ষায় সমতল কাঁচের প্লেটের পরিবর্তে যদি একই বক্রতার ব্যাসার্ধ $R$-এর আরেকটি উত্তল লেন্সের বক্রপৃষ্ঠের ওপর প্রথম লেন্সটি রাখা হয়, তবে বলয়ের ব্যাস কেমন পরিবর্তিত হবে?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>উভয় লেন্সের বক্রপৃষ্ঠ মুখোমুখি রাখলে কার্যকর বক্রতার ব্যাসার্ধ $\frac{1}{R_{\text{eff}}} = \frac{1}{R_1} + \frac{1}{R_2} = \frac{1}{R} + \frac{1}{R} = \frac{2}{R} \Rightarrow R_{\text{eff}} = \frac{R}{2}$। তখন ফিল্মের পুরুত্ব দ্বিগুণ হারে বাড়বে। ব্যাসের সমীকরণ $D_n' = 2\sqrt{n R_{\text{eff}}\lambda} = 2\sqrt{n \frac{R}{2} \lambda} = \frac{D_n}{\sqrt{2}}$। অর্থাৎ বলয়গুলোর ব্যাস মূল ব্যাসের $\frac{1}{\sqrt{2}}$ গুণ হয়ে সংকুচিত হবে।</t>
@@ -3654,7 +3414,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (সমস্যা 1)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3663,35 +3423,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##
-[সমস্যা 1: দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ]
-##PRESET:interference-slits[size:medium]##
-একটি দ্বি-চির পরীক্ষায় চির দুটির মধ্যবর্তী দূরত্ব $d = 0.4\text{ mm}$ এবং চির হতে পর্দার দূরত্ব $D = 1.3\text{ m}$। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $\lambda = 6000\text{ \AA}$ হলে পর্দায় পরপর দুটি উজ্জ্বল ডোরার মধ্যকার দূরত্ব (ডোরা প্রস্থ, $\beta$) কত?</t>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##
+ইয়ং-এর দ্বি-চির পরীক্ষায় চির দুটির মধ্যবর্তী দূরত্ব $d = 0.40\text{ mm}$ এবং চির হতে পর্দার দূরত্ব $D = 1.20\text{ m}$। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $\lambda = 6000\text{ Å} = 600\text{ nm}$ হলে: (ক) পরপর দুটি উজ্জ্বল ডোরার কেন্দ্রদ্বয়ের মধ্যবর্তী দূরত্ব (ডোরা প্রস্থ $\beta$), (খ) কেন্দ্রীয় উজ্জ্বল ডোরা হতে ৪র্থ উজ্জ্বল ডোরার দূরত্ব $y_4$, এবং (গ) ৩য় অন্ধকার ডোরার দূরত্ব $y_3'$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##</t>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 1)।</t>
+          <t>ডোরা প্রস্থ $\beta = \frac{\lambda D}{d} = \frac{(6.0 \times 10^{-7}\text{ m}) \times 1.20\text{ m}}{0.40 \times 10^{-3}\text{ m}} = \frac{7.2 \times 10^{-7}}{4.0 \times 10^{-4}} = 1.80 \times 10^{-3}\text{ m} = 1.80\text{ mm}$। ৪র্থ উজ্জ্বল ডোরার অবস্থান $y_4 = 4\beta = 4 \times 1.80 = 7.20\text{ mm}$। ৩য় অন্ধকার ডোরা ($n = 3$): $y_3' = \left(3 - \frac{1}{2}\right)\beta = 2.5 \times 1.80 = 4.50\text{ mm}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(ক) ডোরা প্রস্থ $\beta = 1.80\text{ mm}$, (খ) ৪র্থ উজ্জ্বল ডোরার দূরত্ব $y_4 = 7.20\text{ mm}$, (গ) ৩য় অন্ধকার ডোরার দূরত্ব $y_3' = 4.50\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3711,12 +3465,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ (সমস্যা 2)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3724,25 +3478,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ]
-প্রতি সেন্টিমিটারে $600$ টি রেখা বিশিষ্ট একটি অপবর্তন গ্রেটিং-এর ওপর লম্বভাবে $\lambda = 5890\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলো আপতিত হলে ১ম ক্রমের উজ্জ্বল পট্টির জন্য অপবর্তন কোণ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি দ্বি-চির পরীক্ষায় আলোর তরঙ্গদৈর্ঘ্য $\lambda = 500\text{ nm}$। চির দুটির মধ্যবর্তী দূরত্ব $d = 0.25\text{ mm}$ হলে ব্যতিচার ডোরার কৌণিক প্রস্থ (Angular fringe width $\theta$) রেডিয়ান ও ডিগ্রিতে নির্ণয় কর। পর্দার দূরত্বের ওপর $\theta$ কীভাবে নির্ভর করে?</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 2)।</t>
+          <t>কৌণিক ডোরা প্রস্থ $\theta = \frac{\beta}{D} = \frac{\lambda}{d} = \frac{500 \times 10^{-9}\text{ m}}{0.25 \times 10^{-3}\text{ m}} = 2.0 \times 10^{-3}\text{ rad}$। ডিগ্রিতে রূপান্তর: $\theta = 2.0 \times 10^{-3} \times \frac{180^\circ}{\pi} \approx 0.11459^\circ \approx 0.115^\circ$। লক্ষ্যণীয় যে সমীকরণে $D$ না থাকায় কৌণিক প্রস্থ পর্দার দূরত্বের ওপর নির্ভরশীল নয়।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>কৌণিক প্রস্থ $\theta = 2.0 \times 10^{-3}\text{ rad} \approx 0.1146^\circ$ (পর্দার দূরত্ব $D$-এর ওপর স্বাধীন/অনির্ভরশীল)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3762,7 +3516,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>একক চিরের ফ্রনহফার অপবর্তন (সমস্যা 3)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3771,29 +3525,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: একক চিরের ফ্রনহফার অপবর্তন]
-$a = 0.8\text{ mm}$ প্রস্থের একটি একক চিরের ওপর $\lambda = 6000\text{ \AA}$ আলো লম্বভাবে আপতিত হলো। চির হতে $D = 1.0\text{ m}$ দূরে রক্ষিত পর্দায় কেন্দ্রীয় চরমের রৈখিক বেধ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি দ্বি-চির ব্যবস্থার সমগ্র অংশকে পানিতে ($n = 1.33 = 4/3$) নিমজ্জিত করা হলো। বায়ুতে ব্যতিচার ডোরার প্রস্থ $\beta_0 = 0.60\text{ mm}$ হলে পানিতে নতুন ডোরা প্রস্থ $\beta'$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 3)।</t>
+          <t>পানিতে আলোর তরঙ্গদৈর্ঘ্য হ্রাস পায়: $\lambda' = \lambda/n$। ফলে ডোরা প্রস্থ $\beta' = \frac{\lambda' D}{d} = \frac{\beta_0}{n} = \frac{0.60\text{ mm}}{4/3} = 0.60 \times \frac{3}{4} = 0.45\text{ mm}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>পানিতে ডোরা প্রস্থ $\beta' = 0.45\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3813,12 +3567,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ (সমস্যা 4)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3826,25 +3580,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ]
-ইয়ং-এর দ্বি-চির পরীক্ষার একটি আলোর গতিপথে $\mu = 1.5$ এবং বেধ $t = 10 \times 10^{-6}\text{ m}$ বিশিষ্ট একটি পাতলা কাচের পাত প্রবেশ করালে ব্যতিচার ঝালর কত দূরত্বে সরে যাবে? ($D = 1\text{ m}, d = 1\text{ mm}$)</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দ্বি-চির পরীক্ষায় ব্যবহৃত দুটি সুসংগত উৎসের তীব্রতার অনুপাত $I_1 : I_2 = 9 : 1$। উৎপন্ন ব্যতিচার প্যাটার্নে উজ্জ্বল ও অন্ধকার পট্টির সর্বোচ্চ ও সর্বনিম্ন তীব্রতার অনুপাত $I_{\max} : I_{\min}$ কত?</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 4)।</t>
+          <t>বিস্তার অনুপাত $\frac{A_1}{A_2} = \sqrt{\frac{I_1}{I_2}} = \sqrt{\frac{9}{1}} = 3$। সর্বোচ্চ তীব্রতা $I_{\max} \propto (A_1 + A_2)^2 = (3 + 1)^2 = 16$। সর্বনিম্ন তীব্রতা $I_{\min} \propto (A_1 - A_2)^2 = (3 - 1)^2 = 4$। অনুপাত $\frac{I_{\max}}{I_{\min}} = \frac{16}{4} = \frac{4}{1} = 4 : 1$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>$I_{\max} : I_{\min} = 4 : 1$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3864,7 +3618,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>আলোর সমবর্তন ও ব্রুস্টারের সূত্র (সমস্যা 5)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3873,29 +3627,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: আলোর সমবর্তন ও ব্রুস্টারের সূত্র]
-কাচের প্রতিসরাঙ্ক $\mu = 1.12$। কাচের পৃষ্ঠে আলো কোন আপতন কোণে আপতিত হলে প্রতিফলিত আলো সম্পূর্ণ সমবর্তিত হবে? (ব্রুস্টারের কোণ $i_p = \tan^{-1}\mu$)</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি দ্বি-চির পরীক্ষায় পর্দার একটি নির্দিষ্ট বিন্দুতে দুটি তরঙ্গের মধ্যবর্তী পথ পার্থক্য $\Delta x = \frac{7}{4}\lambda$। ওই বিন্দুতে তরঙ্গদ্বয়ের দশা পার্থক্য $\Delta\phi$ এবং আলোর তীব্রতা সর্বোচ্চ তীব্রতার শতকরা কত অংশ হবে?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 5)।</t>
+          <t>দশা পার্থক্য $\Delta\phi = \frac{2\pi}{\lambda}\Delta x = \frac{2\pi}{\lambda}\left(\frac{7}{4}\lambda\right) = \frac{7\pi}{2} = 3\pi + \frac{\pi}{2}$। তীব্রতা সমীকরণ: $I = I_{\max}\cos^2\left(\frac{\Delta\phi}{2}\right) = I_{\max}\cos^2\left(\frac{7\pi}{4}\right) = I_{\max}\left(\frac{1}{\sqrt{2}}\right)^2 = \frac{1}{2}I_{\max} = 0.50 I_{\max}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>দশা পার্থক্য $\Delta\phi = \frac{7\pi}{2}\text{ rad} = 630^\circ$, তীব্রতা $I = 0.50 I_{\max}$ ($50\%$ তীব্রতা)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3915,12 +3669,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত (সমস্যা 6)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3928,25 +3682,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত]
-ব্যতিচার সৃষ্টিকারী দুটি সুসঙ্গত উৎসের তীব্রতার অনুপাত $I_1 : I_2 = 2 : 1$। পর্দায় গঠিত চরম ও অবম তীব্রতার অনুপাত ($I_{max} : I_{min}$) কত হবে?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+দ্বি-চির পরীক্ষায় চির দুটির ব্যবধান অর্ধেক ($d/2$) এবং পর্দা হতে চিরের দূরত্ব দ্বিগুণ ($2D$) করা হলে ব্যতিচার ডোরার প্রস্থ আদি মানের কত গুণ হবে?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 6)।</t>
+          <t>ডোরা প্রস্থ $\beta = \frac{\lambda D}{d}$। নতুন ডোরা প্রস্থ $\beta' = \frac{\lambda(2D)}{(d/2)} = 4 \frac{\lambda D}{d} = 4\beta$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>ডোরা প্রস্থ $4.0$ গুণ বৃদ্ধি পাবে</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3966,7 +3720,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম (সমস্যা 7)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3975,29 +3729,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম]
-প্রতি মিলিমিটারে $400$ টি দাগযুক্ত একটি গ্রেটিং দ্বারা $\lambda = 5000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলোর জন্য সর্বোচ্চ কততম ক্রমের স্পেকট্রাম দেখা সম্ভব? ($n_{max} \le d/\lambda$)</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+দ্বি-চির পরীক্ষায় দুটি ভিন্ন তরঙ্গদৈর্ঘ্য $\lambda_1 = 600\text{ nm}$ এবং $\lambda_2 = 480\text{ nm}$ একত্রে ব্যবহার করা হলো। কেন্দ্রীয় উজ্জ্বল ডোরা হতে কততম উজ্জ্বল ডোরায় উভয় তরঙ্গদৈর্ঘ্যের ডোরা প্রথম একে অপরের ওপর সমপাতিত হবে?</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 7)।</t>
+          <t>সমপাতনের শর্ত: $y_{n1} = y_{n2} \implies n_1 \frac{\lambda_1 D}{d} = n_2 \frac{\lambda_2 D}{d} \implies n_1 \lambda_1 = n_2 \lambda_2 \implies \frac{n_1}{n_2} = \frac{\lambda_2}{\lambda_1} = \frac{480}{600} = \frac{4}{5}$। সুতরাং $\lambda_1$-এর ৪র্থ উজ্জ্বল ডোরা এবং $\lambda_2$-এর ৫ম উজ্জ্বল ডোরা একই স্থানে উপরিপাতিত হবে।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>$\lambda_1$-এর ৪র্থ উজ্জ্বল ডোরা $\lambda_2$-এর ৫ম উজ্জ্বল ডোরার সাথে সমপাতিত হবে</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4017,12 +3771,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা (সমস্যা 8)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4030,25 +3784,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা]
-দুটি পোলারয়েড পরস্পর $\theta = 60^\circ$ কোণে আনত রাখা আছে। ১ম পোলারয়েড থেকে নির্গত সমবর্তিত আলোর তীব্রতা $I_0$ হলে ২য় পোলারয়েড দিয়ে নির্গত আলোর তীব্রতা $I = I_0 \cos^2\theta$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি দ্বি-চির পরীক্ষায় পর্দার ওপর $1.0\text{ cm}$ পরিসরে $20$টি ডোরা দেখা যায়। যদি আলোর তরঙ্গদৈর্ঘ্য $600\text{ nm}$ এবং চিরদ্বয়ের ব্যবধান $0.60\text{ mm}$ হয়, তবে চির হতে পর্দার দূরত্ব $D$ কত মিটার?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 8)।</t>
+          <t>ডোরা প্রস্থ $\beta = \frac{1.0\text{ cm}}{20} = \frac{0.010\text{ m}}{20} = 5.0 \times 10^{-4}\text{ m}$। $\beta = \frac{\lambda D}{d} \implies D = \frac{\beta d}{\lambda} = \frac{(5.0 \times 10^{-4}\text{ m}) \times (0.60 \times 10^{-3}\text{ m})}{6.0 \times 10^{-7}\text{ m}} = \frac{3.0 \times 10^{-7}}{6.0 \times 10^{-7}} = 0.50\text{ m}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>পর্দার দূরত্ব $D = 0.50\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4068,7 +3822,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য (সমস্যা 9)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,29 +3831,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য]
-একটি মাইকেলসন ইন্টারফেরোমিটারের একটি দর্পণকে $d = 0.8\text{ mm}$ সরালে দৃষ্টি ক্ষেত্র দিয়ে $900$ টি ব্যতিচার ফ্রিন্জ সরে যায়। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য কত?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ব্যতিচারের জন্য সুসংগত উৎস (Coherent sources) কী এবং কেন দুটি সম্পূর্ণ পৃথক স্বাধীন বাতি বা মোমবাতি ব্যবহার করে ব্যতিচার ডোরা দেখা যায় না?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 9)।</t>
+          <t>স্বাধীন উৎসের পরমাণুগুলো সম্পূর্ণ অসংলগ্নভাবে এলোমেলো দশায় আলো বিকিরণ করে। ফলে প্রতি সেকেন্ডে কোটি কোটি বার দশা পার্থক্য আকস্মিকভাবে পরিবর্তিত হয়। মানুষের চোখের রেটিনার দৃষ্টি স্থায়িত্বকাল ($\approx 0.1\text{ s}$) থাকায় এই অতি দ্রুত পরিবর্তন চোখ ধরতে পারে না এবং কেবলমাত্র একটি গড় সুষম আলোকোজ্জ্বলতা দেখতে পায়; কোনো স্থায়ী ব্যতিচার নকশা দৃশ্যমান হয় না।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>উৎসদ্বয়ের কম্পাঙ্ক অভিন্ন এবং দশা পার্থক্য সময় নিরপেক্ষ ধ্রুবক হতে হয়; স্বাধীন উৎসে লক্ষ লক্ষ পরমাণুর অনিয়মিত ফোটন নিঃসরণে দশা প্রতি ন্যানোসেকেন্ডে পরিবর্তিত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4119,12 +3873,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>তরঙ্গের আলোক পথ ও জ্যামিতিক পথ (সমস্যা 10)</t>
+          <t>ইয়ং-এর দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (Young Double Slit Experiment)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4132,25 +3886,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: তরঙ্গের আলোক পথ ও জ্যামিতিক পথ]
-$\mu = 1.10$ প্রতিসরাঙ্কের $t = 2\text{ cm}$ পুরু একটি কাচ ব্লকের মধ্য দিয়ে আলো অতিক্রম করতে যে সময় নেয়, সম-সময়ে শূন্যস্থানে আলো কত দূরত্ব অতিক্রম করবে?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ব্যতিচারে শক্তির সংরক্ষণশীলতা: ব্যতিচার প্রক্রিয়ায় অন্ধকার ডোরায় আলোর তীব্রতা শূন্য হয়ে যায়। এই অন্ধকার অংশের শক্তি কি ধ্বংস হয়ে যায়? শক্তির রূপান্তর ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 10)।</t>
+          <t>ব্যতিচারে কোনো শক্তি সৃষ্টি বা ধ্বংস হয় না; এটি কেবল আলোর শক্তির এক স্থান হতে অন্য স্থানে পুনর্বণ্টন (Redistribution of energy)। দুটি উৎসের পৃথক তীব্রতা $I_0 + I_0 = 2I_0$। ব্যতিচারের পর উজ্জ্বল ডোরায় তীব্রতা $4I_0$ এবং অন্ধকার ডোরায় শূন্য। সম্পূর্ণ চক্রের গড় তীব্রতা $\frac{4I_0 + 0}{2} = 2I_0$, যা সুসংগত উৎসের মোট শক্তির হুবহু সমান—ফলে শক্তির নিত্যতা সংরক্ষিত থাকে।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>শক্তি ধ্বংস হয় না; অন্ধকার ডোরা হতে শক্তি স্থানান্তরিত হয়ে উজ্জ্বল ডোরায় পুনর্বণ্টিত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4170,44 +3924,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (সমস্যা 11)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##
-[সমস্যা 11: দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ]
-##PRESET:interference-slits[size:medium]##
-একটি দ্বি-চির পরীক্ষায় চির দুটির মধ্যবর্তী দূরত্ব $d = 0.12\text{ mm}$ এবং চির হতে পর্দার দূরত্ব $D = 1.3\text{ m}$। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $\lambda = 6000\text{ \AA}$ হলে পর্দায় পরপর দুটি উজ্জ্বল ডোরার মধ্যকার দূরত্ব (ডোরা প্রস্থ, $\beta$) কত?</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+দ্বি-চির পরীক্ষার একটি চিরের সামনে $t = 1.2 \times 10^{-5}\text{ m}$ পুরু এবং $n = 1.50$ প্রতিসরাঙ্কের একটি পাতলা মাইকা পাত রাখা হলো। $\lambda = 600\text{ nm}$ আলোর ক্ষেত্রে কেন্দ্রীয় উজ্জ্বল ডোরাটি কতটি ডোরার সমান দূরত্ব সরে যাবে (Fringe shift)?</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 11)।</t>
+          <t>মাইকা পাতের কারণে অতিরিক্ত পথ পার্থক্য $\Delta x = (n - 1)t$। ডোরার সরণ সংখ্যা $N = \frac{\Delta x}{\lambda} = \frac{(n - 1)t}{\lambda} = \frac{(1.50 - 1) \times (1.2 \times 10^{-5}\text{ m})}{6.0 \times 10^{-7}\text{ m}} = \frac{0.50 \times 1.2 \times 10^{-5}}{6.0 \times 10^{-7}} = \frac{6.0 \times 10^{-6}}{6.0 \times 10^{-7}} = 10$। অতএব প্যাটার্নটি ১০টি ডোরার সমান দূরত্ব সরে যাবে।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>ডোরা সরণ $N = 10$ টি ডোরা</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4227,7 +3975,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ (সমস্যা 12)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4240,25 +3988,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ]
-প্রতি সেন্টিমিটারে $200$ টি রেখা বিশিষ্ট একটি অপবর্তন গ্রেটিং-এর ওপর লম্বভাবে $\lambda = 5890\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলো আপতিত হলে ১ম ক্রমের উজ্জ্বল পট্টির জন্য অপবর্তন কোণ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি পাতলা সাবান পানির বুদবুদ স্তরের ($n = 1.33$) ওপর লম্বভাবে সাদা আলো আপতিত হলো। প্রতিফলিত আলোতে $\lambda = 532\text{ nm}$ আলো গঠনমূলক ব্যতিচারের মাধ্যমে উজ্জ্বলভাবে দৃশ্যমান হয়। স্তরটির ন্যূনতম বেধ $t_{\min}$ কত?</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 12)।</t>
+          <t>ঘন মাধ্যম পৃষ্ঠের প্রতিফলনে অতিরিক্ত $\lambda/2$ পথ পার্থক্য যুক্ত হয়। পাতলা স্তরে প্রতিফলিত আলোর গঠনমূলক ব্যতিচারের শর্ত: $2 n t = \left(m - \frac{1}{2}\right)\lambda$। ন্যূনতম বেধের জন্য $m = 1$: $2 n t_{\min} = \frac{1}{2}\lambda \implies t_{\min} = \frac{\lambda}{4n} = \frac{532\text{ nm}}{4(1.33)} = \frac{532}{5.32} = 100.0\text{ nm}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>ন্যূনতম বেধ $t_{\min} = 100.0\text{ nm}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4278,38 +4026,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>একক চিরের ফ্রনহফার অপবর্তন (সমস্যা 13)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: একক চিরের ফ্রনহফার অপবর্তন]
-$a = 0.4\text{ mm}$ প্রস্থের একটি একক চিরের ওপর $\lambda = 6000\text{ \AA}$ আলো লম্বভাবে আপতিত হলো। চির হতে $D = 1.0\text{ m}$ দূরে রক্ষিত পর্দায় কেন্দ্রীয় চরমের রৈখিক বেধ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি একক চিরের প্রস্থ $a = 0.20\text{ mm}$। চিরটির ওপর $\lambda = 500\text{ nm}$ তরঙ্গদৈর্ঘ্যের সমান্তরাল আলো লম্বভাবে আপতিত হলো। ফ্রনহফার অপবর্তনে প্রথম অবম বিন্দুর (1st minimum) অপবর্তন কোণ $\theta_1$ এবং দ্বিতীয় চরম বিন্দুর (2nd secondary maximum) অপবর্তন কোণ কত?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 13)।</t>
+          <t>একক চিরে অপবর্তন অবম শর্ত: $a\sin\theta = n\lambda$। ১ম অবমে ($n = 1$): $\sin\theta_1 \approx \theta_1 = \frac{\lambda}{a} = \frac{500 \times 10^{-9}}{0.20 \times 10^{-3}} = 2.50 \times 10^{-3}\text{ rad} \approx 0.1432^\circ$। ২য় গৌণ চরম ($n = 2$): $a\sin\theta = \left(2 + \frac{1}{2}\right)\lambda = 2.5\lambda \implies \theta \approx \frac{2.5\lambda}{a} = 2.5(2.5 \times 10^{-3}) = 6.25 \times 10^{-3}\text{ rad} \approx 0.358^\circ$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>১ম অবমের কোণ $\theta_1 = 2.50 \times 10^{-3}\text{ rad} \approx 0.143^\circ$, ২য় গৌণ চরমের কোণ $\theta \approx 6.25 \times 10^{-3}\text{ rad} \approx 0.358^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4329,7 +4077,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ (সমস্যা 14)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4342,25 +4090,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ]
-ইয়ং-এর দ্বি-চির পরীক্ষার একটি আলোর গতিপথে $\mu = 1.5$ এবং বেধ $t = 6 \times 10^{-6}\text{ m}$ বিশিষ্ট একটি পাতলা কাচের পাত প্রবেশ করালে ব্যতিচার ঝালর কত দূরত্বে সরে যাবে? ($D = 1\text{ m}, d = 1\text{ mm}$)</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একক চিরের ফ্রনহফার অপবর্তনে চিরের প্রস্থ $a = 0.10\text{ mm}$, আলোর তরঙ্গদৈর্ঘ্য $\lambda = 600\text{ nm}$ এবং চির হতে পর্দার দূরত্ব $D = 2.0\text{ m}$। কেন্দ্রীয় উজ্জ্বল পট্টির রৈখিক প্রস্থ (Linear width of central maximum $2y$) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 14)।</t>
+          <t>কেন্দ্রীয় চরমের কৌণিক বিস্তার দুই পাশের ১ম অবম পর্যন্ত: $2\theta = \frac{2\lambda}{a}$। রৈখিক প্রস্থ $2y = D(2\theta) = \frac{2\lambda D}{a} = \frac{2(6.0 \times 10^{-7}\text{ m})(2.0\text{ m})}{0.10 \times 10^{-3}\text{ m}} = \frac{2.4 \times 10^{-6}}{1.0 \times 10^{-4}} = 0.024\text{ m} = 2.40\text{ cm}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>কেন্দ্রীয় পট্টির রৈখিক প্রস্থ $2y = 2.40\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4380,38 +4128,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>আলোর সমবর্তন ও ব্রুস্টারের সূত্র (সমস্যা 15)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: আলোর সমবর্তন ও ব্রুস্টারের সূত্র]
-কাচের প্রতিসরাঙ্ক $\mu = 1.8$। কাচের পৃষ্ঠে আলো কোন আপতন কোণে আপতিত হলে প্রতিফলিত আলো সম্পূর্ণ সমবর্তিত হবে? (ব্রুস্টারের কোণ $i_p = \tan^{-1}\mu$)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি একক চিরের অপবর্তন প্যাটার্নে কেন্দ্রীয় চরমের তীব্রতা $I_0$। ১ম গৌণ চরমের তীব্রতা প্রায় $rac{I_0}{22}$ বা $4.5\%$ এবং ২য় গৌণ চরমের তীব্রতা প্রায় $rac{I_0}{61}$ বা $1.6\%$—তীব্রতা তীব্রভাবে হ্রাস পাওয়ার কারণ কী?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 15)।</t>
+          <t>১ম গৌণ চরমে চিরটিকে ৩টি সমান অঞ্চলে ভাগ করা যায় যার মধ্যে দুটি অঞ্চল পরস্পরের আলোকে ধ্বংস করে, ফলে মাত্র $1/3$ অংশের বিস্তার কার্যকর থাকে; তীব্রতা $I \propto (A_0/3)^2 \approx I_0/9$ (নিখুঁত সংহত বিশ্লেষণে $\left(\frac{\sin\beta}{\beta}\right)^2 \approx \frac{I_0}{(3\pi/2)^2} = \frac{I_0}{22.2} \approx 4.5\%$)। ২য় গৌণ চরমে মাত্র $1/5$ অংশ কার্যকর থাকে, ফলে তীব্রতা দ্রুত হ্রাস পায়।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>চিরকে ৩টি, ৫টি ইত্যাদি বিজোড় সমান অংশে ভাগ করলে কেবল ১টি অংশের আলো অবশিষ্ট থাকে এবং বাকি অংশগুলো পরস্পরের সাথে ধ্বংসাত্মক উপরিপাতনে বাতিল হয়</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4431,7 +4179,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত (সমস্যা 16)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4444,25 +4192,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত]
-ব্যতিচার সৃষ্টিকারী দুটি সুসঙ্গত উৎসের তীব্রতার অনুপাত $I_1 : I_2 = 10 : 1$। পর্দায় গঠিত চরম ও অবম তীব্রতার অনুপাত ($I_{max} : I_{min}$) কত হবে?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+ব্যতিচার ও অপবর্তনের মধ্যকার মৌলিক পার্থক্য কী? একটি দ্বি-চির পরীক্ষায় প্রকৃতপক্ষে এই দুই ঘটনার সম্মিলিত রূপ কীভাবে দেখা যায়?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 16)।</t>
+          <t>ব্যতিচারে দুটি চির হতে নির্গত সুসংগত তরঙ্গের উপরিপাতনে সমপ্রস্থের ডোরা সৃষ্টি হয়। অপবর্তনে একটি উন্মেষের বিভিন্ন বিন্দু হতে উৎপন্ন অসংখ্য গৌণ তরঙ্গের উপরিপাতনে অসমপ্রস্থ ও দ্রুত তীব্রতা হ্রাসপ্রাপ্ত নকশা গঠিত হয়। বাস্তব দ্বি-চির পরীক্ষায় একক চিরের অপবর্তন এনভেলপের (Diffraction envelope) ভেতরে একাধিক সূক্ষ্ম ব্যতিচার ডোরা অবস্থান করে।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>ব্যতিচার হলো সসীম সংখ্যক পৃথক তরঙ্গমুখের উপরিপাতন; অপবর্তন হলো একই তরঙ্গমুখের অবিচ্ছিন্ন গৌণ তরঙ্গের উপরিপাতন</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4482,38 +4230,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম (সমস্যা 17)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম]
-প্রতি মিলিমিটারে $1200$ টি দাগযুক্ত একটি গ্রেটিং দ্বারা $\lambda = 5000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলোর জন্য সর্বোচ্চ কততম ক্রমের স্পেকট্রাম দেখা সম্ভব? ($n_{max} \le d/\lambda$)</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি দ্বি-চির ব্যবস্থায় চিরের প্রস্থ $a = 0.04\text{ mm}$ এবং চিরদ্বয়ের মধ্যবর্তী ব্যবধান $d = 0.20\text{ mm}$। কেন্দ্রীয় অপবর্তন চরমের ভেতরে কতটি পূর্ণ ব্যতিচার ডোরা অবস্থান করবে?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 17)।</t>
+          <t>কেন্দ্রীয় অপবর্তন চরমের কৌণিক বিস্তার $2\theta_d = \frac{2\lambda}{a}$। একটি ব্যতিচার ডোরার কৌণিক প্রস্থ $\theta_i = \frac{\lambda}{d}$। কেন্দ্রীয় চরমের ভেতর ডোরার সংখ্যা $N = \frac{2\theta_d}{\theta_i} = \frac{2\lambda/a}{\lambda/d} = \frac{2d}{a} = \frac{2(0.20)}{0.04} = \frac{0.40}{0.04} = 10$। যেহেতু ১০ম ক্রমের ব্যতিচার উজ্জ্বল ডোরাটি অপবর্তনের ১ম অবমের সাথে হুবহু মিলে অদৃশ্য হয়ে যায় (Missing order), তাই কেন্দ্রীয় অঞ্চলে ৯টি স্পষ্ট ডোরা দৃশ্যমান থাকে।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>কেন্দ্রীয় অপবর্তন চরমের ভেতর মোট $10$টি ব্যতিচার ডোরা থাকবে (বা $9$টি স্পষ্ট ডোরা)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4533,7 +4281,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা (সমস্যা 18)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4546,25 +4294,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা]
-দুটি পোলারয়েড পরস্পর $\theta = 20^\circ$ কোণে আনত রাখা আছে। ১ম পোলারয়েড থেকে নির্গত সমবর্তিত আলোর তীব্রতা $I_0$ হলে ২য় পোলারয়েড দিয়ে নির্গত আলোর তীব্রতা $I = I_0 \cos^2\theta$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=4][size:small]##
+একটি সাবান পানির উলম্ব ফিল্মের শীর্ষদেশে ব্যতিচারের অন্ধকার অংশ দেখা যায় কেন? (নিউটন রিং বা সাবান ফিল্মের শূন্য বেধ বিশ্লেষণ)।</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 18)।</t>
+          <t>উল্লম্ব ফিল্মে তরল নিচের দিকে নেমে যাওয়ায় শীর্ষে বেধ অত্যন্ত নগণ্য ($t \ll \lambda$) হয়। ফলে জ্যামিতিক পথ পার্থক্য $2nt \approx 0$। কিন্তু প্রথম পৃষ্ঠে আলো ঘন মাধ্যমে প্রতিফলিত হওয়ায় $\pi$ দশা পরিবর্তন বা $\lambda/2$ পথ পার্থক্য লাভ করে। ফলে নিট পথ পার্থক্য হয় $\lambda/2$, যা ধ্বংসাত্মক ব্যতিচারের শর্ত তৈরি করে ফিল্মের শীর্ষভাগকে সম্পূর্ণ অন্ধকার দেখায়।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>শীর্ষে ফিল্মের বেধ $t \to 0$ হওয়ায় পথ পার্থক্য কেবল প্রতিফলনে সৃষ্ট $\lambda/2$; ফলে সম্পূর্ণ ধ্বংসাত্মক ব্যতিচার ঘটে</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4584,38 +4332,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য (সমস্যা 19)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য]
-একটি মাইকেলসন ইন্টারফেরোমিটারের একটি দর্পণকে $d = 0.4\text{ mm}$ সরালে দৃষ্টি ক্ষেত্র দিয়ে $900$ টি ব্যতিচার ফ্রিন্জ সরে যায়। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য কত?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+র্যালির অপবর্তন মানদণ্ড (Rayleigh's Criterion of Resolution): কখন দুটি নিকটবর্তী বিন্দু উৎসকে একটি অপটিক্যাল যন্ত্র দ্বারা সবেমাত্র পৃথকীকরণযোগ্য (Just resolved) বলা হয়?</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 19)।</t>
+          <t>লর্ড র্যালির প্রস্তাবনা অনুসারে দুটি অভিন্ন উৎস তখনই পৃথক করা যায় যখন তাদের কেন্দ্রীয় উজ্জ্বল চরমদ্বয়ের কেন্দ্র ব্যবধান অন্তত ১ম অন্ধকার অবমের দূরত্বের সমান হয়। তখন লব্ধি তীব্রতার মাঝে প্রায় $19\%$ খাদ সৃষ্টি হয় যা মানুষের চোখ বা সেন্সর দ্বারা দুটি স্বতন্ত্র বস্তু হিসেবে শনাক্ত করা সম্ভব হয়।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>যখন একটি উৎসের অপবর্তন প্যাটার্নের কেন্দ্রীয় চরম ঠিক অপর উৎসের ১ম অবম বিন্দুর ওপর সমপাতিত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4635,7 +4383,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>তরঙ্গের আলোক পথ ও জ্যামিতিক পথ (সমস্যা 20)</t>
+          <t>একক চিরের অপবর্তন ও বিভেদন সীমা (Diffraction &amp; Resolution Limit)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4648,25 +4396,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: তরঙ্গের আলোক পথ ও জ্যামিতিক পথ]
-$\mu = 1.6$ প্রতিসরাঙ্কের $t = 2\text{ cm}$ পুরু একটি কাচ ব্লকের মধ্য দিয়ে আলো অতিক্রম করতে যে সময় নেয়, সম-সময়ে শূন্যস্থানে আলো কত দূরত্ব অতিক্রম করবে?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+মানুষের চোখের তারারন্ধ্রের ব্যাস $D = 4.0\text{ mm}$ এবং দৃশ্যমান আলোর গড় তরঙ্গদৈর্ঘ্য $\lambda = 550\text{ nm}$। চোখের ন্যূনতম কৌণিক বিভেদন সীমা (Angular resolution) কত রেডিয়ান ও আর্ক-মিনিটে নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 20)।</t>
+          <t>বৃত্তাকার উন্মেষের জন্য র্যালির সূত্র: $\theta = \frac{1.22\lambda}{D} = \frac{1.22 \times (550 \times 10^{-9}\text{ m})}{4.0 \times 10^{-3}\text{ m}} = \frac{6.71 \times 10^{-7}}{4.0 \times 10^{-3}} = 1.6775 \times 10^{-4}\text{ rad}$। আর্ক-মিনিটে: $\theta = 1.6775 \times 10^{-4} \times \left(\frac{180 \times 60}{\pi}\right) \approx 0.5767'\text{ arcmin}$ (যা প্রায় ১ আর্ক-মিনিটের সমান)।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>বিভেদন সীমা $\theta \approx 1.678 \times 10^{-4}\text{ rad} \approx 0.577'\text{ arcmin} \approx 1'\text{ arcmin}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4686,44 +4434,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (সমস্যা 21)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##
-[সমস্যা 21: দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ]
-##PRESET:interference-slits[size:medium]##
-একটি দ্বি-চির পরীক্ষায় চির দুটির মধ্যবর্তী দূরত্ব $d = 0.8\text{ mm}$ এবং চির হতে পর্দার দূরত্ব $D = 1.3\text{ m}$। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $\lambda = 6000\text{ \AA}$ হলে পর্দায় পরপর দুটি উজ্জ্বল ডোরার মধ্যকার দূরত্ব (ডোরা প্রস্থ, $\beta$) কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি অপবর্তন গ্রেটিং-এ প্রতি সেন্টিমিটারে $5000$টি রেখা আছে। $\lambda = 600\text{ nm}$ আলো লম্বভাবে আপতিত হলে: (ক) গ্রেটিং ধ্রুবক (Grating element $d$), (খ) প্রথম ও দ্বিতীয় ক্রমের অপবর্তন কোণ $\theta_1$ ও $\theta_2$, এবং (গ) এই তরঙ্গদৈর্ঘ্যে সর্বোচ্চ কততম ক্রম ($n_{\max}$) দেখা সম্ভব নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 21)।</t>
+          <t>গ্রেটিং উপাদান $d = \frac{1}{N} = \frac{1\text{ cm}}{5000} = \frac{10^{-2}\text{ m}}{5000} = 2.0 \times 10^{-6}\text{ m}$। গ্রেটিং সমীকরণ: $d\sin\theta = n\lambda$। ১ম ক্রম ($n = 1$): $\sin\theta_1 = \frac{\lambda}{d} = \frac{600 \times 10^{-9}}{2.0 \times 10^{-6}} = 0.30 \implies \theta_1 = \arcsin(0.30) \approx 17.458^\circ$। ২য় ক্রম ($n = 2$): $\sin\theta_2 = \frac{2\lambda}{d} = 0.60 \implies \theta_2 = \arcsin(0.60) \approx 36.87^\circ$। সর্বোচ্চ ক্রমের জন্য $\sin\theta \le 1 \implies n \le \frac{d}{\lambda} = \frac{2.0 \times 10^{-6}}{6.0 \times 10^{-7}} = 3.33 \implies n_{\max} = 3$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>(ক) গ্রেটিং ধ্রুবক $d = 2.0 \times 10^{-6}\text{ m}$, (খ) $\theta_1 = 17.46^\circ, \theta_2 = 36.87^\circ$, (গ) সর্বোচ্চ ক্রম $n_{\max} = 3$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4743,12 +4485,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ (সমস্যা 22)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4756,25 +4498,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ]
-প্রতি সেন্টিমিটারে $1000$ টি রেখা বিশিষ্ট একটি অপবর্তন গ্রেটিং-এর ওপর লম্বভাবে $\lambda = 5890\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলো আপতিত হলে ১ম ক্রমের উজ্জ্বল পট্টির জন্য অপবর্তন কোণ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গ্রেটিং-এর সাহায্যে সোডিয়াম আলোর দুটি নিকটবর্তী হলুদ রেখা $\lambda_1 = 589.0\text{ nm}$ এবং $\lambda_2 = 589.6\text{ nm}$-কে দ্বিতীয় ক্রমের বর্ণালীতে ($n = 2$) পৃথকভাবে শনাক্ত করতে গ্রেটিংটিতে ন্যূনতম মোট কতটি রেখা ($N_{\text{total}}$) থাকতে হবে?</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 22)।</t>
+          <t>গ্রেটিং-এর বিভেদন ক্ষমতা: $\frac{\lambda}{\Delta\lambda} = n N_{\text{total}}$। গড় তরঙ্গদৈর্ঘ্য $\lambda = 589.3\text{ nm}$, পার্থক্য $\Delta\lambda = 0.6\text{ nm}$। বিভেদন ক্ষমতা $\frac{\lambda}{\Delta\lambda} = \frac{589.3}{0.6} \approx 982.17$। দ্বিতীয় ক্রমে ($n = 2$): $2 N_{\text{total}} = 982.17 \implies N_{\text{total}} = \frac{982.17}{2} \approx 491.08 \implies$ ন্যূনতম ৪৯১টি রেখা আলোকিত হতে হবে।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>ন্যূনতম রেখা সংখ্যা $N_{\text{total}} = 491$ টি</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4794,38 +4536,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>একক চিরের ফ্রনহফার অপবর্তন (সমস্যা 23)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: একক চিরের ফ্রনহফার অপবর্তন]
-$a = 0.12\text{ mm}$ প্রস্থের একটি একক চিরের ওপর $\lambda = 6000\text{ \AA}$ আলো লম্বভাবে আপতিত হলো। চির হতে $D = 1.0\text{ m}$ দূরে রক্ষিত পর্দায় কেন্দ্রীয় চরমের রৈখিক বেধ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##
+একটি সমতল অপবর্তন গ্রেটিং-এ প্রতি মিলিমিটারে $600$টি রেখা রয়েছে। সাদা আলো লম্বভাবে আপতিত হলে লাল আলোর ($\lambda_R = 700\text{ nm}$) ১ম ক্রমের বর্ণালী রেখা এবং বেগুনি আলোর ($\lambda_V = 400\text{ nm}$) ২য় ক্রমের বর্ণালী রেখার মধ্যে কৌণিক বিচ্ছেদ কত ডিগ্রি?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 23)।</t>
+          <t>$d = \frac{1\text{ mm}}{600} = \frac{10^{-3}\text{ m}}{600} = \frac{1}{6} \times 10^{-5}\text{ m} \approx 1.667 \times 10^{-6}\text{ m}$। লাল আলোর ১ম ক্রম: $\sin\theta_R = \frac{1 \times 7.0 \times 10^{-7}}{1.6667 \times 10^{-6}} = 0.420 \implies \theta_R = \arcsin(0.420) \approx 24.83^\circ$। বেগুনি আলোর ২য় ক্রম: $\sin\theta_V = \frac{2 \times 4.0 \times 10^{-7}}{1.6667 \times 10^{-6}} = 0.480 \implies \theta_V = \arcsin(0.480) \approx 28.69^\circ$। কৌণিক বিচ্ছেদ $\Delta\theta = 28.69^\circ - 24.83^\circ = 3.86^\circ$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>কৌণিক বিচ্ছেদ $\Delta\theta = 3.86^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4845,12 +4587,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ (সমস্যা 24)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4858,25 +4600,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ]
-ইয়ং-এর দ্বি-চির পরীক্ষার একটি আলোর গতিপথে $\mu = 1.5$ এবং বেধ $t = 2 \times 10^{-6}\text{ m}$ বিশিষ্ট একটি পাতলা কাচের পাত প্রবেশ করালে ব্যতিচার ঝালর কত দূরত্বে সরে যাবে? ($D = 1\text{ m}, d = 1\text{ mm}$)</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+ম্যালাসের সূত্রানুযায়ী (Malus's Law) একটি পোলারাইজার ও অ্যানালাইজারের অক্ষের মধ্যবর্তী কোণ $\theta = 60^\circ$। আপতিত সমতল সমবর্তিত আলোর তীব্রতা $I_0$ হলে অ্যানালাইজার হতে নির্গত আলোর তীব্রতা কত হবে?</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 24)।</t>
+          <t>ম্যালাসের সূত্র: $I = I_0 \cos^2\theta = I_0 \cos^2(60^\circ) = I_0 (0.5)^2 = 0.25 I_0 = \frac{1}{4}I_0$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>নির্গমন তীব্রতা $I = 0.25 I_0 = \frac{1}{4}I_0$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4896,38 +4638,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>আলোর সমবর্তন ও ব্রুস্টারের সূত্র (সমস্যা 25)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: আলোর সমবর্তন ও ব্রুস্টারের সূত্র]
-কাচের প্রতিসরাঙ্ক $\mu = 1.4$। কাচের পৃষ্ঠে আলো কোন আপতন কোণে আপতিত হলে প্রতিফলিত আলো সম্পূর্ণ সমবর্তিত হবে? (ব্রুস্টারের কোণ $i_p = \tan^{-1}\mu$)</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি অসমবর্তিত (Unpolarized) আলোর রশ্মি পর পর তিনটি পোলারয়েড $P_1, P_2, P_3$-এর মধ্য দিয়ে যায়। $P_1$ ও $P_3$ পরস্পরের সাথে আড়াআড়ি (Crossed, $	heta = 90^\circ$)। এদের মাঝে $P_2$-কে $P_1$-এর সাথে $45^\circ$ কোণে রাখা হলো। নির্গত আলোর তীব্রতা আদি তীব্রতা $I_0$-এর কত শতাংশ?</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 25)।</t>
+          <t>অসমবর্তিত আলো $P_1$ পার হলে তীব্রতা $I_1 = I_0/2$। $P_2$-এর অক্ষ $P_1$-এর সাথে $45^\circ$ হওয়ায় $I_2 = I_1 \cos^2(45^\circ) = \frac{I_0}{2} \times \frac{1}{2} = \frac{I_0}{4}$। $P_3$-এর অক্ষ $P_2$-এর সাথে কোণ $= 90^\circ - 45^\circ = 45^\circ$। ফলে $P_3$ পার হওয়ার পর তীব্রতা $I_3 = I_2 \cos^2(45^\circ) = \frac{I_0}{4} \times \frac{1}{2} = \frac{I_0}{8} = 0.125 I_0 = 12.5\%$। (যদি $P_2$ না থাকত তবে কোনো আলো পার হতো না)।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>চূড়ান্ত নির্গত তীব্রতা $I = 0.125 I_0 = 12.5\%$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4947,12 +4689,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত (সমস্যা 26)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4960,25 +4702,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত]
-ব্যতিচার সৃষ্টিকারী দুটি সুসঙ্গত উৎসের তীব্রতার অনুপাত $I_1 : I_2 = 6 : 1$। পর্দায় গঠিত চরম ও অবম তীব্রতার অনুপাত ($I_{max} : I_{min}$) কত হবে?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি কাচ পাতের প্রতিসরাঙ্ক $n = 1.60$। বাতাসে কাচ পাতের ওপর আলো আপতিত হলে ব্রুস্টারের সমবর্তন কোণ (Polarizing angle $i_p$) কত? এই আপতন কোণে প্রতিসরণ কোণ $r_p$ কত?</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 26)।</t>
+          <t>ব্রুস্টারের সূত্র: $\tan i_p = n = 1.60 \implies i_p = \arctan(1.60) \approx 57.99^\circ \approx 58.0^\circ$। ব্রুস্টার কোণে প্রতিফলিত ও প্রতিসরিত রশ্মি পরস্পরের ওপর লম্ব: $i_p + r_p = 90^\circ \implies r_p = 90^\circ - 58.0^\circ = 32.0^\circ$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>সমবর্তন কোণ $i_p = 58.0^\circ$, প্রতিসরণ কোণ $r_p = 32.0^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4998,38 +4740,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম (সমস্যা 27)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম]
-প্রতি মিলিমিটারে $800$ টি দাগযুক্ত একটি গ্রেটিং দ্বারা $\lambda = 5000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলোর জন্য সর্বোচ্চ কততম ক্রমের স্পেকট্রাম দেখা সম্ভব? ($n_{max} \le d/\lambda$)</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+আলোক সক্রিয়তা ও পোলারিমিটার: একটি চিনির দ্রবণের ঘনত্ব $c = 0.20\text{ g/cm}^3$। $L = 2.0\text{ dm} = 20\text{ cm}$ দৈর্ঘ্যের একটি নলের মধ্য দিয়ে সোডিয়াম আলো পাঠালে আলোর সমবর্তন তল $\theta = 26.4^\circ$ কোণে আবর্তিত হয়। চিনির আপেক্ষিক আবর্তন (Specific rotation $S$) কত ডিগ্রি/($	ext{dm}\cdot\text{g/cm}^3$)?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 27)।</t>
+          <t>আপেক্ষিক আবর্তনের সমীকরণ: $S = \frac{\theta}{L \times c}$। মান বসিয়ে: $S = \frac{26.4^\circ}{2.0\text{ dm} \times 0.20\text{ g/cm}^3} = \frac{26.4}{0.40} = +66.0^\circ$। (এটি প্রমাণ সুক্রোজের আপেক্ষিক আবর্তন নির্দেশ করে)।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>আপেক্ষিক আবর্তন $S = +66.0^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5049,12 +4791,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা (সমস্যা 28)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5062,25 +4804,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা]
-দুটি পোলারয়েড পরস্পর $\theta = 100^\circ$ কোণে আনত রাখা আছে। ১ম পোলারয়েড থেকে নির্গত সমবর্তিত আলোর তীব্রতা $I_0$ হলে ২য় পোলারয়েড দিয়ে নির্গত আলোর তীব্রতা $I = I_0 \cos^2\theta$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+দ্বি-প্রতিসরণ (Double Refraction / Birefringence) এবং নিকল প্রিজম: ক্যালসাইট কেলাসে আপতিত আলোক রশ্মি দুটি প্রতিসরিত রশ্মিতে বিভক্ত হয়—সাধারণ রশ্মি (O-ray) ও অসাধারণ রশ্মি (E-ray)। এদের মধ্যকার মৌলিক পার্থক্য কী?</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 28)।</t>
+          <t>ক্যালসাইট স্ফটিকের অ্যানিসোট্রপিক প্রকৃতির কারণে O-রশ্মির ক্ষেত্রে প্রতিসরাঙ্ক $n_o$ ধ্রুব থাকে এবং এর তরঙ্গমুখ গোলীয় হয়। কিন্তু E-রশ্মির বৈদ্যুতিক ভেক্টর অপটিক অক্ষের সাথে বিভিন্ন কোণে ক্রিয়া করায় এর প্রতিসরাঙ্ক $n_e$ এবং বেগ বিভিন্ন দিকে পরিবর্তিত হয়, ফলে এর তরঙ্গমুখ উপবৃত্তীয় হয়। নিকল প্রিজমে কানাডা বালসাম আস্তরণ দ্বারা O-রশ্মিকে পূর্ণ অভ্যন্তরীণ প্রতিফলনে বাদ দিয়ে কেবল E-রশ্মিকে সমতল সমবর্তিত আলো হিসেবে নির্গত করা হয়।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>সাধারণ রশ্মি (O-ray) স্নেলের প্রতিসরণ সূত্র সম্পূর্ণ মেনে চলে এবং এর বেগ সব দিকে সমান; অসাধারণ রশ্মি (E-ray) স্নেলের সূত্র মানে না এবং এর বেগ দিক-নির্ভরশীল</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5100,38 +4842,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য (সমস্যা 29)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য]
-একটি মাইকেলসন ইন্টারফেরোমিটারের একটি দর্পণকে $d = 0.12\text{ mm}$ সরালে দৃষ্টি ক্ষেত্র দিয়ে $900$ টি ব্যতিচার ফ্রিন্জ সরে যায়। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য কত?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+কোয়ার্টার ওয়েভ প্লেট (Quarter-wave plate, QWP) এবং হাফ ওয়েভ প্লেটের (HWP) বেধের সমীকরণ প্রতিপাদন কর। $\lambda = 600\text{ nm}$, $n_o = 1.55$ এবং $n_e = 1.54$ বিশিষ্ট ধনাত্মক কেলাসের জন্য QWP-এর ন্যূনতম বেধ কত?</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 29)।</t>
+          <t>O-রশ্মি ও E-রশ্মির মধ্যে পথ পার্থক্য $\Delta x = |n_o - n_e|t$। QWP-এর জন্য পথ পার্থক্য $\lambda/4$ হতে হবে: $|n_o - n_e|t = \frac{\lambda}{4} \implies t = \frac{\lambda}{4|n_o - n_e|} = \frac{600 \times 10^{-9}}{4(1.55 - 1.54)} = \frac{600 \times 10^{-9}}{4(0.01)} = \frac{600 \times 10^{-9}}{0.04} = 1.50 \times 10^{-5}\text{ m} = 15.0\text{ }\mu\text{m}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>QWP বেধ $t = \frac{\lambda}{4|n_o - n_e|} = 1.50 \times 10^{-5}\text{ m} = 15.0\text{ }\mu\text{m}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5151,12 +4893,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>তরঙ্গের আলোক পথ ও জ্যামিতিক পথ (সমস্যা 30)</t>
+          <t>অপবর্তন গ্রেটিং ও সমবর্তন (Diffraction Grating &amp; Polarization)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5164,25 +4906,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: তরঙ্গের আলোক পথ ও জ্যামিতিক পথ]
-$\mu = 1.2$ প্রতিসরাঙ্কের $t = 2\text{ cm}$ পুরু একটি কাচ ব্লকের মধ্য দিয়ে আলো অতিক্রম করতে যে সময় নেয়, সম-সময়ে শূন্যস্থানে আলো কত দূরত্ব অতিক্রম করবে?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+বৃত্তীয় সমবর্তিত আলো (Circularly polarized light) এবং উপবৃত্তীয় সমবর্তিত আলো (Elliptically polarized light) কীভাবে সৃষ্টি করা যায়?</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 30)।</t>
+          <t>সমতল সমবর্তিত আলো একটি কোয়ার্টার ওয়েভ প্লেটে অপটিক অক্ষের সাথে $45^\circ$ কোণে আপতিত হলে O-ray ও E-ray-এর বিস্তার সমান হয় ($A_o = A_e$) এবং এদের মধ্যে $\pi/2$ ($90^\circ$) দশা পার্থক্য যুক্ত হয়ে লব্ধি ভেক্টর একটি বৃত্তাকার ঘূর্ণন সম্পন্ন করে (বৃত্তীয় সমবর্তন)। কোণ $45^\circ$ ব্যতীত অন্য কোণ হলে বিস্তার অসমান হওয়ায় উপবৃত্তাকার ক্ষেত্র তৈরি হয়।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>সমান বিস্তারের দুটি সমকোণীয় সমতল সমবর্তিত তরঙ্গের মাঝে $\pi/2$ দশা পার্থক্য থাকলে বৃত্তীয় আলো সৃষ্টি হয়; বিস্তার অসমান হলে উপবৃত্তীয় আলো হয়</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5202,44 +4944,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (সমস্যা 31)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##
-[সমস্যা 31: দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ]
-##PRESET:interference-slits[size:medium]##
-একটি দ্বি-চির পরীক্ষায় চির দুটির মধ্যবর্তী দূরত্ব $d = 0.4\text{ mm}$ এবং চির হতে পর্দার দূরত্ব $D = 1.3\text{ m}$। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $\lambda = 6000\text{ \AA}$ হলে পর্দায় পরপর দুটি উজ্জ্বল ডোরার মধ্যকার দূরত্ব (ডোরা প্রস্থ, $\beta$) কত?</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি দ্বি-চির পরীক্ষায় আলোর তরঙ্গদৈর্ঘ্য $600\text{ nm}$ এবং চিরের ব্যবধান $0.5\text{ mm}$। পর্দাটি চির হতে $1.0\text{ m}$ দূরে অবস্থিত। কেন্দ্রীয় উজ্জ্বল ডোরার ঠিক বিপরীতে একটি চিরের সামনে কত বেধের গ্লাস স্ল্যাব ($n = 1.50$) রাখলে কেন্দ্রীয় উজ্জ্বল ডোরাটি পূর্বে যেখানে ৫ম উজ্জ্বল ডোরা ছিল সেখানে স্থানান্তরিত হবে?</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 31)।</t>
+          <t>৫ম উজ্জ্বল ডোরার স্থানান্তরের জন্য পথ পার্থক্য $\Delta x = 5\lambda$ হতে হবে: $(n - 1)t = 5\lambda \implies (1.50 - 1)t = 5(6.0 \times 10^{-7}\text{ m}) \implies 0.50 t = 3.0 \times 10^{-6}\text{ m} \implies t = \frac{3.0 \times 10^{-6}}{0.50} = 6.0 \times 10^{-6}\text{ m} = 6.0\text{ }\mu\text{m}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>স্ল্যাবের বেধ $t = 6.0\\text{ }\mu\text{m}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5259,12 +4995,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ (সমস্যা 32)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5272,25 +5008,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ]
-প্রতি সেন্টিমিটারে $600$ টি রেখা বিশিষ্ট একটি অপবর্তন গ্রেটিং-এর ওপর লম্বভাবে $\lambda = 5890\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলো আপতিত হলে ১ম ক্রমের উজ্জ্বল পট্টির জন্য অপবর্তন কোণ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি অপবর্তন গ্রেটিং-এ দৃশ্যমান আলোর পরিসরে ($400\text{ nm}$ হতে $700\text{ nm}$) ২য় ক্রমের বর্ণালীর সাথে ৩য় ক্রমের কোনো অংশ কি উপরিপাতিত হবে? গাণিতিকভাবে বিশ্লেষণ কর।</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 32)।</t>
+          <t>গ্রেটিং সমীকরণ: $d\sin\theta = n\lambda$। ২য় ক্রমের দীর্ঘতম তরঙ্গদৈর্ঘ্য $\lambda_2 = 700\text{ nm} \implies d\sin\theta = 2(700) = 1400\text{ nm}$। ৩য় ক্রমের ক্ষেত্রে: $3\lambda_3 = 1400 \implies \lambda_3 = \frac{1400}{3} \approx 466.7\text{ nm}$। যেহেতু $466.7\text{ nm}$ দৃশ্যমান পরিসরের মধ্যে ($400\text{ nm}$-এর চেয়ে বড়), তাই ২য় ক্রমের লাল প্রান্ত এবং ৩য় ক্রমের বেগুনি প্রান্ত একই কোণে উপরিপাতিত হয়ে ওভারল্যাপিং সৃষ্টি করে।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>হ্যাঁ, ২য় ক্রমের লাল প্রান্ত ($600-700\text{ nm}$) ৩য় ক্রমের বেগুনি-নীল প্রান্তের ($400-466.7\text{ nm}$) সাথে উপরিপাতিত হবে</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5310,38 +5046,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>একক চিরের ফ্রনহফার অপবর্তন (সমস্যা 33)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: একক চিরের ফ্রনহফার অপবর্তন]
-$a = 0.8\text{ mm}$ প্রস্থের একটি একক চিরের ওপর $\lambda = 6000\text{ \AA}$ আলো লম্বভাবে আপতিত হলো। চির হতে $D = 1.0\text{ m}$ দূরে রক্ষিত পর্দায় কেন্দ্রীয় চরমের রৈখিক বেধ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##
+হাইজেনের নীতি দ্বারা আলোর প্রতিফলনের সূত্র প্রমাণ কর: দেখাও যে আপতিত তরঙ্গমুখ এবং প্রতিফলিত তরঙ্গমুখের জ্যামিতি থেকে আপতন কোণ = প্রতিফলন কোণ ($i = r$)।</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 33)।</t>
+          <t>আপতিত সমতল তরঙ্গমুখ $AB$ প্রতিফলক তলের সাথে $i$ কোণে আপতিত হয়। গৌণ তরঙ্গমুখ $t$ সময়ে $BC = v t$ দূরত্ব অতিক্রম করতে করতে $A$ বিন্দু হতে গৌণ তরঙ্গগোলক $v t$ ব্যাসার্ধে পৌঁছায়। ত্রিভুজ $\triangle ABC$ এবং $\triangle ADC$ সর্বসম হওয়ায় (উভয়ে সমকোণী এবং অতিভুজ $AC$ সাধারণ ও $BC = AD = vt$), কোণ $\angle BAC = \angle DCA \implies i = r$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>আপতন কোণ $i = r$ (প্রতিফলন সূত্র প্রমাণিত)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5361,12 +5097,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ (সমস্যা 34)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5374,25 +5110,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ]
-ইয়ং-এর দ্বি-চির পরীক্ষার একটি আলোর গতিপথে $\mu = 1.5$ এবং বেধ $t = 10 \times 10^{-6}\text{ m}$ বিশিষ্ট একটি পাতলা কাচের পাত প্রবেশ করালে ব্যতিচার ঝালর কত দূরত্বে সরে যাবে? ($D = 1\text{ m}, d = 1\text{ mm}$)</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি অপবর্তন গ্রেটিং-এ প্রতি ইঞ্চিতে $15000$টি রেখা আছে ($1\text{ inch} = 2.54\text{ cm}$)। $\lambda = 500\text{ nm}$ আলোর জন্য প্রথম ক্রমের অপবর্তন কোণ কত?</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 34)।</t>
+          <t>গ্রেটিং উপাদান $d = \frac{2.54 \times 10^{-2}\text{ m}}{15000} \approx 1.6933 \times 10^{-6}\text{ m}$। গ্রেটিং সমীকরণ: $\sin\theta_1 = \frac{\lambda}{d} = \frac{5.0 \times 10^{-7}\text{ m}}{1.6933 \times 10^{-6}\text{ m}} \approx 0.29528 \implies \theta_1 = \arcsin(0.29528) \approx 17.175^\circ \approx 17.18^\circ$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>১ম ক্রমের কোণ $\theta_1 = 17.18^\circ$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5412,38 +5148,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>আলোর সমবর্তন ও ব্রুস্টারের সূত্র (সমস্যা 35)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: আলোর সমবর্তন ও ব্রুস্টারের সূত্র]
-কাচের প্রতিসরাঙ্ক $\mu = 1.12$। কাচের পৃষ্ঠে আলো কোন আপতন কোণে আপতিত হলে প্রতিফলিত আলো সম্পূর্ণ সমবর্তিত হবে? (ব্রুস্টারের কোণ $i_p = \tan^{-1}\mu$)</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ফ্রনহফার অপবর্তন পরীক্ষায় একটি বৃত্তাকার ছিদ্রের ব্যাস $D = 0.50\text{ mm}$। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $500\text{ nm}$ এবং পর্দাটি $1.0\text{ m}$ দূরে অবস্থিত হলে কেন্দ্রীয় উজ্জ্বল এয়ারি চাকতির (Airy disk) ব্যাসার্ধ কত মিমি?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 35)।</t>
+          <t>বৃত্তাকার অপবর্তনে ১ম অবমের কৌণিক ব্যাসার্ধ $\theta = \frac{1.22\lambda}{D} = \frac{1.22 \times 500 \times 10^{-9}}{0.50 \times 10^{-3}} = \frac{6.1 \times 10^{-7}}{5.0 \times 10^{-4}} = 1.22 \times 10^{-3}\text{ rad}$। পর্দায় রৈখিক ব্যাসার্ধ $R = D_{\text{screen}} \times \theta = 1.0\text{ m} \times (1.22 \times 10^{-3}\text{ rad}) = 1.22 \times 10^{-3}\text{ m} = 1.22\text{ mm}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>এয়ারি চাকতির ব্যাসার্ধ $R = 1.22\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5463,12 +5199,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত (সমস্যা 36)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5476,25 +5212,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত]
-ব্যতিচার সৃষ্টিকারী দুটি সুসঙ্গত উৎসের তীব্রতার অনুপাত $I_1 : I_2 = 2 : 1$। পর্দায় গঠিত চরম ও অবম তীব্রতার অনুপাত ($I_{max} : I_{min}$) কত হবে?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+পোলারয়েড চশমা কীভাবে ঝলকানি (Glare) দূর করে? অনুভূমিক পৃষ্ঠ (যেমন রাস্তা বা পানি) হতে প্রতিফলিত আলোর সমবর্তনের দিক ব্যাখ্যা কর।</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 36)।</t>
+          <t>ব্রুস্টারের নীতি অনুসারে অনুভূমিক পানির তল বা চকচকে রাস্তা হতে প্রতিফলিত আলো প্রধানত অনুভূমিক দিকে কম্পমান তড়িৎ ভেক্টর ধারণ করে (glare)। পোলারয়েড সানগ্লাসের অক্ষ উল্লম্বভাবে প্রস্তুত করায় এটি অনুভূমিক সমবর্তিত ঝলকানি আলোকে সম্পূর্ণ শোষণ করে বাদ দেয়, কিন্তু উল্লম্ব কম্পনের স্বাভাবিক দৃশ্যমান আলোকে প্রবেশ করতে দেয়।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>অনুভূমিক পৃষ্ঠ হতে প্রতিফলিত আলো অনুভূমিক তলে সমবর্তিত হয়; পোলারয়েড চশমার উল্লম্ব সঞ্চালন অক্ষ এই প্রতিফলিত ঝলকানিকে সম্পূর্ণ আটকে দেয়</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5514,38 +5250,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম (সমস্যা 37)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম]
-প্রতি মিলিমিটারে $400$ টি দাগযুক্ত একটি গ্রেটিং দ্বারা $\lambda = 5000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলোর জন্য সর্বোচ্চ কততম ক্রমের স্পেকট্রাম দেখা সম্ভব? ($n_{max} \le d/\lambda$)</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি দ্বি-চির পরীক্ষায় আলোর দুটি সুসংগত উৎসের বিস্তারের অনুপাত $2:1$। উজ্জ্বল ডোরা ও অন্ধকার ডোরার কন্ট্রাস্ট (Fringe visibility $V = rac{I_{\max} - I_{\min}}{I_{\max} + I_{\min}}$) কত?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 37)।</t>
+          <t>$A_1 = 2, A_2 = 1$। $I_{\max} \propto (2 + 1)^2 = 9$ এবং $I_{\min} \propto (2 - 1)^2 = 1$। ডোরার দৃশ্যমানতা $V = \frac{I_{\max} - I_{\min}}{I_{\max} + I_{\min}} = \frac{9 - 1}{9 + 1} = \frac{8}{10} = 0.80 = 80\%$। (সমান বিস্তার $A_1 = A_2$ হলে $V = 1.0$ বা ১০০% নিখুঁত কন্ট্রাস্ট পাওয়া যেত)।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>ডোরা দৃশ্যমানতা $V = 0.80 = 80\%$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5565,12 +5301,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা (সমস্যা 38)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5578,25 +5314,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা]
-দুটি পোলারয়েড পরস্পর $\theta = 60^\circ$ কোণে আনত রাখা আছে। ১ম পোলারয়েড থেকে নির্গত সমবর্তিত আলোর তীব্রতা $I_0$ হলে ২য় পোলারয়েড দিয়ে নির্গত আলোর তীব্রতা $I = I_0 \cos^2\theta$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+মাইকেলসন ইন্টারফেরোমিটারে (Michelson Interferometer) একটি চলমান দর্পণকে $0.15\text{ mm}$ সরালে দৃষ্টি ক্ষেত্র দিয়ে $500$টি ব্যতিচার ডোরা পার হয়ে যায়। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য কত?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 38)।</t>
+          <t>দর্পণের সরণ $d$ হলে পথ পার্থক্যের পরিবর্তন $\Delta x = 2d$। ডোরার সংখ্যা $N = \frac{2d}{\lambda} \implies \lambda = \frac{2d}{N} = \frac{2 \times (0.15 \times 10^{-3}\text{ m})}{500} = \frac{3.0 \times 10^{-4}}{500} = 6.0 \times 10^{-7}\text{ m} = 600.0\text{ nm}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>তরঙ্গদৈর্ঘ্য $\lambda = 600.0\text{ nm} = 6000\text{ Å}$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5616,38 +5352,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য (সমস্যা 39)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য]
-একটি মাইকেলসন ইন্টারফেরোমিটারের একটি দর্পণকে $d = 0.8\text{ mm}$ সরালে দৃষ্টি ক্ষেত্র দিয়ে $900$ টি ব্যতিচার ফ্রিন্জ সরে যায়। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য কত?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি দ্বি-চির পরীক্ষায় চির দুটির ব্যবধান $d = 1.0\text{ mm}$ এবং পর্দা $D = 1.0\text{ m}$ দূরে। সাদা আলো ($400-700\text{ nm}$) ব্যবহার করলে কেন্দ্রীয় ডোরার বর্ণ কী হবে এবং এর ঠিক পাশে কোন রঙের ডোরা প্রথম দৃশ্যমান হবে?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 39)।</t>
+          <t>কেন্দ্রীয় বিন্দুতে সকল তরঙ্গদৈর্ঘ্যের পথ পার্থক্য শূন্য হওয়ায় সমস্ত বর্ণের গঠনমূলক ব্যতিচার একসাথে ঘটে এবং সাদা রঙ উৎপন্ন হয়। কেন্দ্রীয় চরম হতে দূরত্ব $y = \frac{\lambda D}{d} \propto \lambda$। যেহেতু বেগুনি আলোর তরঙ্গদৈর্ঘ্য সর্বনিম্ন ($\lambda_V \approx 400\text{ nm}$), তাই কেন্দ্রীয় সাদার ঠিক নিকটবর্তী ১ম উজ্জ্বল ডোরাটি বেগুনি বর্ণের হবে এবং সবচেয়ে দূরে লাল রঙের ডোরা থাকবে।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>কেন্দ্রীয় ডোরাটি সম্পূর্ণ সাদা হবে; এর ঠিক পাশেই প্রথমে বেগুনি রঙের ডোরা দেখা যাবে</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5667,12 +5403,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>তরঙ্গের আলোক পথ ও জ্যামিতিক পথ (সমস্যা 40)</t>
+          <t>উন্নত অপটিক্যাল ইন্টারফেরোমেট্রি ও তরঙ্গ আলোকবিজ্ঞান (Advanced Wave Optics)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5680,25 +5416,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: তরঙ্গের আলোক পথ ও জ্যামিতিক পথ]
-$\mu = 1.10$ প্রতিসরাঙ্কের $t = 2\text{ cm}$ পুরু একটি কাচ ব্লকের মধ্য দিয়ে আলো অতিক্রম করতে যে সময় নেয়, সম-সময়ে শূন্যস্থানে আলো কত দূরত্ব অতিক্রম করবে?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+আলোর অপবর্তন ও শব্দের অপবর্তনের তুলনা: দৈনন্দিন জীবনে শব্দের অপবর্তন সহজে প্রত্যক্ষ করা গেলেও আলোর অপবর্তন সাধারণ চোখে সচরাচর ধরা পড়ে না কেন?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 40)।</t>
+          <t>অপবর্তন স্পষ্টভাবে লক্ষ্য করার শর্ত হলো বাধার বা ছিদ্রের আকার তরঙ্গের তরঙ্গদৈর্ঘ্যের সমতুল্য বা কাছাকাছি ($a \approx \lambda$) হতে হয়। শব্দের তরঙ্গদৈর্ঘ্য সাধারণ দরজা-জানালার আকারের সমান হওয়ায় শব্দ সহজে বেঁকে যায়। কিন্তু আলোর তরঙ্গদৈর্ঘ্য মাত্র ৪০০-৭০০ ন্যানোমিটার হওয়ায় অত্যন্ত সূক্ষ্ম চির বা ধারালো ব্লেডের ধার ব্যতীত সাধারণ ঘরের বাধার চারদিকে আলোর অপবর্তন চোখে পড়ার মতো হয় না।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>শব্দের তরঙ্গদৈর্ঘ্য দৈনন্দিন বাধার আকারের সমতুল্য ($\approx 1\text{ m}$), কিন্তু আলোর তরঙ্গদৈর্ঘ্য অত্যন্ত ক্ষুদ্র ($\approx 10^{-7}\text{ m}$)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5718,44 +5454,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ (সমস্যা 41)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##
-[সমস্যা 41: দ্বি-চির ব্যতিচার ও ডোরা প্রস্থ]
-##PRESET:interference-slits[size:medium]##
-একটি দ্বি-চির পরীক্ষায় চির দুটির মধ্যবর্তী দূরত্ব $d = 0.12\text{ mm}$ এবং চির হতে পর্দার দূরত্ব $D = 1.3\text{ m}$। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $\lambda = 6000\text{ \AA}$ হলে পর্দায় পরপর দুটি উজ্জ্বল ডোরার মধ্যকার দূরত্ব (ডোরা প্রস্থ, $\beta$) কত?</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি একক চির অপবর্তনে ১ম অবমের জন্য চিরটিকে দুটি অর্ধেকে ভাগ করে পথ পার্থক্য $\lambda/2$ বিবেচনা করা হয়। কেন কেন্দ্রীয় চরমের ক্ষেত্রে ধ্বংসাত্মক উপরিপাতন ঘটে না?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:interference-slits[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 41)।</t>
+          <t>অক্ষের ওপর লম্বভাবে সরাসরি নির্গত সমস্ত তরঙ্গমুখের কণাগুলোর মধ্যে কোনো পথ পার্থক্য থাকে না ($\Delta x = 0 \implies \Delta\phi = 0$)। ফলে চিরের প্রতিটি বিন্দু হতে আগত সমস্ত গৌণ তরঙ্গ পরস্পরের সাথে গঠনমূলকভাবে যুক্ত হয়, যা কেন্দ্রীয় অঞ্চলে সর্বোচ্চ তীব্রতা সৃষ্টি করে।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>কেন্দ্রীয় চরমে চিরের সমস্ত অংশ হতে আগত গৌণ তরঙ্গগুলোর পথ পার্থক্য শূন্য হওয়ায় এরা সমদশায় মিলিত হয়ে সর্বোচ্চ উজ্জ্বলতা গঠন করে</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5775,12 +5505,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ (সমস্যা 42)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5788,25 +5518,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: অপবর্তন গ্রেটিং ও উজ্জ্বল চরম কোণ]
-প্রতি সেন্টিমিটারে $200$ টি রেখা বিশিষ্ট একটি অপবর্তন গ্রেটিং-এর ওপর লম্বভাবে $\lambda = 5890\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলো আপতিত হলে ১ম ক্রমের উজ্জ্বল পট্টির জন্য অপবর্তন কোণ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+নিউটন রিং (Newton's Rings) পরীক্ষায় প্রতিফলিত আলোতে কেন্দ্রীয় স্পটটি অন্ধকার দেখায় কেন এবং তলদেশে প্রতিসরাঙ্ক $n_f &gt; n_{	ext{glass}}$ তরল দিলে কেন্দ্রের কী ঘটবে?</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 42)।</t>
+          <t>বায়ুস্তরে নিচের সমতল কাচ হতে প্রতিফলনের সময় ঘন মাধ্যমের কারণে $\pi$ দশা পরিবর্তন ঘটে, ফলে স্পর্শবিন্দুতে ($t = 0$) পথ পার্থক্য $\lambda/2$ হয়ে ধ্বংসাত্মক ব্যতিচারে অন্ধকার সৃষ্টি হয়। কিন্তু যদি কাচের চেয়ে বেশি প্রতিসরাঙ্কের তরল প্রবেশ করানো হয়, তবে লেন্সের তলদেশ হতেই $\pi$ দশা পরিবর্তন ঘটে যায়; ফলে উভয় পৃষ্ঠের দশা পরিবর্তন একই হওয়ায় কেন্দ্রটি উজ্জ্বল দেখাবে।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>কেন্দ্রীয় স্পর্শবিন্দুতে কাচ-বায়ু প্রতিফলনে $\pi$ দশা পরিবর্তনে অন্ধকার স্পট হয়; উচ্চ প্রতিসরাঙ্কের তরল দিলে উভয় প্রতিফলনে একই দশা পরিবর্তন হয়ে কেন্দ্র উজ্জ্বল হবে</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5826,38 +5556,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>একক চিরের ফ্রনহফার অপবর্তন (সমস্যা 43)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: একক চিরের ফ্রনহফার অপবর্তন]
-$a = 0.4\text{ mm}$ প্রস্থের একটি একক চিরের ওপর $\lambda = 6000\text{ \AA}$ আলো লম্বভাবে আপতিত হলো। চির হতে $D = 1.0\text{ m}$ দূরে রক্ষিত পর্দায় কেন্দ্রীয় চরমের রৈখিক বেধ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি গ্রেটিং-এর ১ম ক্রমের বর্ণালীতে হলুদ ও সবুজ আলোর কৌণিক বিচ্ছুরণ $rac{d	heta}{d\lambda} = rac{n}{d\cos	heta}$। দেখাও যে ক্ষুদ্র কোণে বিচ্ছুরণ বর্ণালী প্রায় সমদূরত্বে রৈখিক থাকে।</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 43)।</t>
+          <t>প্রিজমে বিচ্ছুরণ তরঙ্গদৈর্ঘ্যের সাথে ব্যস্তানুপাতিক ($\frac{dn}{d\lambda} \propto \frac{1}{\lambda^3}$) হওয়ায় বেগুনি প্রান্ত খুব বেশি প্রসারিত এবং লাল প্রান্ত সংকুচিত থাকে। কিন্তু গ্রেটিং-এ $\theta$ ক্ষুদ্র হলে $\cos\theta \approx 1$, ফলে কৌণিক বিচ্ছুরণ ধ্রুবক থাকে এবং বর্ণালীর সমস্ত রঙ সুষমভাবে বিস্তৃত থাকে (স্বাভাবিক বর্ণালী বা Normal spectrum)।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>ক্ষুদ্র কোণে $\cos\theta \approx 1 \implies \frac{d\theta}{d\lambda} \approx \frac{n}{d} = \text{ধ্রুবক}$ (সাধারণ প্রিজমের চেয়ে অনেক সুষম)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5877,12 +5607,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ (সমস্যা 44)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5890,25 +5620,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: পাতলা স্বচ্ছ পাত প্রবেশে ব্যতিচার ফ্রিন্জ সরণ]
-ইয়ং-এর দ্বি-চির পরীক্ষার একটি আলোর গতিপথে $\mu = 1.5$ এবং বেধ $t = 6 \times 10^{-6}\text{ m}$ বিশিষ্ট একটি পাতলা কাচের পাত প্রবেশ করালে ব্যতিচার ঝালর কত দূরত্বে সরে যাবে? ($D = 1\text{ m}, d = 1\text{ mm}$)</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পোলারাইজার ও অ্যানালাইজারের মাঝে একটি কোয়ার্টার ওয়েভ প্লেট এমনভাবে রাখা হলো যাতে এর অপটিক অক্ষ পোলারাইজারের সাথে $45^\circ$ কোণে থাকে। অ্যানালাইজারকে ঘোরালে নির্গত আলোর তীব্রতার কী পরিবর্তন হবে?</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 44)।</t>
+          <t>পোলারাইজার হতে নির্গত সমতল সমবর্তিত আলো কোয়ার্টার ওয়েভ প্লেটে $45^\circ$-এ প্রবেশ করলে এটি নিখুঁত বৃত্তীয় সমবর্তিত আলোতে (Circularly polarized light) রূপান্তরিত হয়। বৃত্তীয় আলোর তড়িৎ ভেক্টরের বিস্তার চতুর্দিকে সমান হওয়ায় অ্যানালাইজারকে যে কোনো কোণে ঘোরালেও অভিক্ষিপ্ত উপাংশের বর্গ ধ্রুব থাকে, ফলে তীব্রতার কোনো হ্রাস-বৃদ্ধি ঘটে না।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>অ্যানালাইজারকে যে কোনো কোণে ঘোরালেও নির্গত তীব্রতা সম্পূর্ণ অপরিবর্তিত ধ্রুব থাকবে</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5928,38 +5658,39 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>আলোর সমবর্তন ও ব্রুস্টারের সূত্র (সমস্যা 45)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: আলোর সমবর্তন ও ব্রুস্টারের সূত্র]
-কাচের প্রতিসরাঙ্ক $\mu = 1.8$। কাচের পৃষ্ঠে আলো কোন আপতন কোণে আপতিত হলে প্রতিফলিত আলো সম্পূর্ণ সমবর্তিত হবে? (ব্রুস্টারের কোণ $i_p = \tan^{-1}\mu$)</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি দ্বি-চির পরীক্ষায় আলোর তীব্রতার বিস্তার ফাংশন $I(	heta) = I_0 \cos^2(eta) \left(rac{\sinlpha}{lpha}+ight)^2$ যেখানে $eta = rac{\pi d}{\lambda}\sin	heta$ এবং $lpha = rac{\pi a}{\lambda}\sin	heta$। এই সূত্রের ভৌত তাৎপর্য বিশ্লেষণ কর।</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 45)।</t>
+          <t>বাস্তব দ্বি-চির প্যাটার্ন হলো একক চিরের অপবর্তন ফ্র্যাকশন দ্বারা মড্যুলেট হওয়া ব্যতিচার ডোরার সমষ্টি। প্রতিটি চিরের সসীম প্রস্থ $a$ থাকার কারণে অপবর্তন এনভেলপ বিস্তৃত হয় এবং কেন্দ্র হতে দূরবর্তী ব্যতিচার ডোরার উজ্জ্বলতা দ্রুত ম্লান হয়ে যায়।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>$\cos^2\beta$ পদটি দুই চিরের ব্যতিচার নির্দেশ করে এবং $\left(\frac{\sin\alpha}{\alpha}\right)^2$ পদটি প্রতিটি চিরের নিজস্ব অপবর্তন এনভেলপ নির্দেশ করে</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5979,12 +5710,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত (সমস্যা 46)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5992,25 +5723,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: ব্যতিচারে তরঙ্গদ্বয়ের তীব্রতার অনুপাত]
-ব্যতিচার সৃষ্টিকারী দুটি সুসঙ্গত উৎসের তীব্রতার অনুপাত $I_1 : I_2 = 10 : 1$। পর্দায় গঠিত চরম ও অবম তীব্রতার অনুপাত ($I_{max} : I_{min}$) কত হবে?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি ফ্রনহফার অপবর্তন পরীক্ষায় চিরের প্রস্থ $a = 0.40\text{ mm}$। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য $\lambda = 500\text{ nm}$। চির হতে $1.5\text{ m}$ দূরে রক্ষিত পর্দায় ১ম ও ২য় অবম বিন্দুর মধ্যবর্তী দূরত্ব নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 46)।</t>
+          <t>অবম বিন্দুর অবস্থান $y_n = n \frac{\lambda D}{a}$। ১ম ও ২য় অবমের মধ্যবর্তী দূরত্ব $\Delta y = y_2 - y_1 = \frac{\lambda D}{a} = \frac{(500 \times 10^{-9}\text{ m}) \times 1.5\text{ m}}{0.40 \times 10^{-3}\text{ m}} = \frac{7.5 \times 10^{-7}}{4.0 \times 10^{-4}} = 1.875 \times 10^{-3}\text{ m} = 1.875\text{ mm}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>ব্যবধান $\Delta y = 1.875\text{ mm}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6030,38 +5761,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম (সমস্যা 47)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: গ্রেটিং-এর সর্বোচ্চ অপবর্তন ক্রম]
-প্রতি মিলিমিটারে $1200$ টি দাগযুক্ত একটি গ্রেটিং দ্বারা $\lambda = 5000\text{ \AA}$ তরঙ্গদৈর্ঘ্যের আলোর জন্য সর্বোচ্চ কততম ক্রমের স্পেকট্রাম দেখা সম্ভব? ($n_{max} \le d/\lambda$)</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি চিনির জলীয় দ্রবণের ঘনত্বের শতকরা মান পরিমাপে $20\text{ cm}$ লম্বা টিউবে সমবর্তন তলের আবর্তন পাওয়া গেল $+13.2^\circ$। চিনির আপেক্ষিক আবর্তন $+66^\circ\text{ dm}^{-1}\text{g}^{-1}\text{cm}^3$ হলে দ্রবণের ঘনত্ব কত?</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 47)।</t>
+          <t>টিউবের দৈর্ঘ্য $L = 20\text{ cm} = 2.0\text{ dm}$। আপেক্ষিক আবর্তন $S = \frac{\theta}{L \times c} \implies c = \frac{\theta}{L \times S} = \frac{13.2^\circ}{2.0 \times 66^\circ} = \frac{13.2}{132} = 0.10\text{ g/cm}^3$। অর্থাৎ দ্রবণটির ঘনত্ব ১০%।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>ঘনত্ব $c = 0.10\text{ g/cm}^3 = 10.0\%$ দ্রবণ</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6081,12 +5812,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা (সমস্যা 48)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6094,25 +5825,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: ম্যালুসের সূত্র ও সমবর্তিত আলোর তীব্রতা]
-দুটি পোলারয়েড পরস্পর $\theta = 20^\circ$ কোণে আনত রাখা আছে। ১ম পোলারয়েড থেকে নির্গত সমবর্তিত আলোর তীব্রতা $I_0$ হলে ২য় পোলারয়েড দিয়ে নির্গত আলোর তীব্রতা $I = I_0 \cos^2\theta$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি অপবর্তন গ্রেটিং-এ প্রতি মিলিমিটারে $500$টি দাগ আছে। দৃশ্যমান আলোর কোন তরঙ্গদৈর্ঘ্যের জন্য ৩য় ক্রমের অপবর্তন কোণ $90^\circ$ হবে?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 48)।</t>
+          <t>$d = \frac{1\text{ mm}}{500} = 2.0 \times 10^{-6}\text{ m}$। ৩য় ক্রমে $\theta = 90^\circ \implies \sin 90^\circ = 1$। গ্রেটিং সমীকরণ: $d \sin 90^\circ = 3\lambda \implies \lambda = \frac{d}{3} = \frac{2.0 \times 10^{-6}\text{ m}}{3} \approx 6.667 \times 10^{-7}\text{ m} = 666.67\text{ nm}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>তরঙ্গদৈর্ঘ্য $\lambda = 666.67\text{ nm}$ (লাল আলো)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6132,38 +5863,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য (সমস্যা 49)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: মাইকেলসন ইন্টারফেরোমিটার ও তরঙ্গদৈর্ঘ্য]
-একটি মাইকেলসন ইন্টারফেরোমিটারের একটি দর্পণকে $d = 0.4\text{ mm}$ সরালে দৃষ্টি ক্ষেত্র দিয়ে $900$ টি ব্যতিচার ফ্রিন্জ সরে যায়। ব্যবহৃত আলোর তরঙ্গদৈর্ঘ্য কত?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##
+একটি অপবর্তন গ্রেটিং-এ আলোর অপবর্তন কোণ $	heta$ হলে নির্গত আলোর তরঙ্গদৈর্ঘ্যের পরিবর্তনের সাথে কৌণিক বিচ্যুতির পরিবর্তনের হার (Angular dispersion) $rac{d	heta}{d\lambda} = rac{n}{d\cos	heta}$ প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:triangle[b=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 49)।</t>
+          <t>গ্রেটিং সমীকরণ: $d\sin\theta = n\lambda$। তরঙ্গদৈর্ঘ্য $\lambda$-এর সাপেক্ষে উভয়পক্ষে ব্যবকলন করে: $d\cos\theta \frac{d\theta}{d\lambda} = n \implies \frac{d\theta}{d\lambda} = \frac{n}{d\cos\theta}$। এটি প্রমাণ করে যে উচ্চ ক্রম ($n$) এবং সূক্ষ্ম গ্রেটিং উপাদানের ($d$ ক্ষুদ্র) জন্য কৌণিক বিচ্ছুরণ বৃদ্ধি পায়।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>$\frac{d\theta}{d\lambda} = \frac{n}{d\cos\theta}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6183,12 +5914,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>তরঙ্গের আলোক পথ ও জ্যামিতিক পথ (সমস্যা 50)</t>
+          <t>উন্নত তরঙ্গ অপটিক্স সংশ্লেষণ ও প্রতিপাদন (Advanced Physical Optics Synthesis)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6196,25 +5927,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: তরঙ্গের আলোক পথ ও জ্যামিতিক পথ]
-$\mu = 1.6$ প্রতিসরাঙ্কের $t = 2\text{ cm}$ পুরু একটি কাচ ব্লকের মধ্য দিয়ে আলো অতিক্রম করতে যে সময় নেয়, সম-সময়ে শূন্যস্থানে আলো কত দূরত্ব অতিক্রম করবে?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+লয়েড-এর একক দর্পণ (Lloyd's Mirror) পরীক্ষায় সৃষ্ট ব্যতিচার ডোরার সাথে ইয়ং-এর দ্বি-চির পরীক্ষার মৌলিক পার্থক্য কী?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>আলোর ব্যতিচার, অপবর্তন ও সমবর্তনের তাত্ত্বিক সমীকরণ দ্বারা নিখুঁত সমাধান (সমস্যা 50)।</t>
+          <t>লয়েডের দর্পণে সরাসরি আলো এবং দর্পণে অত্যন্ত সূক্ষ্ম কোণে প্রতিফলিত আলোর উপরিপাতনে ব্যতিচার ঘটে। প্রতিফলিত আলো ঘন কাচ তলে প্রতিফলিত হওয়ায় অতিরিক্ত $\lambda/2$ পথ পার্থক্য বা $\pi$ দশা পরিবর্তন লাভ করে। ফলে স্পর্শবিন্দুতে যেখানে পথ পার্থক্য শূন্য হওয়ার কথা সেখানে একটি অন্ধকার ডোরা গঠিত হয়, যা ইয়ং-এর দ্বি-চিরের সম্পূর্ণ বিপরীত।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>ভৌত আলোকবিজ্ঞানের উত্তর 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>লয়েডের দর্পণে স্পর্শবিন্দুর কেন্দ্রীয় ডোরাটি প্রতিফলনের $\pi$ দশা পরিবর্তনের কারণে অন্ধকার হয় (ইয়ং-এ উজ্জ্বল হয়)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
